--- a/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\projetos\bolão_copa\gabarito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5A672E-E7F5-4BB7-B701-F9351033960A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C802AB-5F92-41D6-8345-F20514458448}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regras" sheetId="1" r:id="rId1"/>
@@ -4976,67 +4976,73 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5045,22 +5051,13 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5076,6 +5073,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5836,7 +5836,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5972,67 +5972,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="273" t="s">
+      <c r="AH3" s="270" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="273" t="s">
+      <c r="AJ3" s="270" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="273" t="s">
+      <c r="AL3" s="270" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="273" t="s">
+      <c r="AN3" s="270" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="273" t="s">
+      <c r="AP3" s="270" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="273" t="s">
+      <c r="AR3" s="270" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="273" t="s">
+      <c r="AT3" s="270" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="273" t="s">
+      <c r="AV3" s="270" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="275" t="s">
+      <c r="AX3" s="274" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="275" t="s">
+      <c r="AZ3" s="274" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="275" t="s">
+      <c r="BB3" s="274" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="275" t="s">
+      <c r="BD3" s="274" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="281" t="s">
+      <c r="BF3" s="277" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="281" t="s">
+      <c r="BH3" s="277" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="279" t="s">
+      <c r="BJ3" s="273" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="280" t="s">
+      <c r="BL3" s="275" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -6041,131 +6041,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="270">
+      <c r="B4" s="272">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="270">
+      <c r="D4" s="272">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="270">
+      <c r="F4" s="272">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="270">
+      <c r="H4" s="272">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="270">
+      <c r="J4" s="272">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="270">
+      <c r="L4" s="272">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="270">
+      <c r="N4" s="272">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="270">
+      <c r="P4" s="272">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="270">
+      <c r="R4" s="272">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="270">
+      <c r="T4" s="272">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="270">
+      <c r="V4" s="272">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="270">
+      <c r="X4" s="272">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="270">
+      <c r="Z4" s="272">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="270">
+      <c r="AB4" s="272">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="270">
+      <c r="AD4" s="272">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="270">
+      <c r="AF4" s="272">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="274">
+      <c r="AH4" s="276">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="274">
+      <c r="AJ4" s="276">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="274">
+      <c r="AL4" s="276">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="274">
+      <c r="AN4" s="276">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="274">
+      <c r="AP4" s="276">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="274">
+      <c r="AR4" s="276">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="274">
+      <c r="AT4" s="276">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="274">
+      <c r="AV4" s="276">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="272">
+      <c r="AX4" s="278">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="272">
+      <c r="AZ4" s="278">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="272">
+      <c r="BB4" s="278">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="272">
+      <c r="BD4" s="278">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="277">
+      <c r="BF4" s="279">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="277">
+      <c r="BH4" s="279">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="276">
+      <c r="BJ4" s="281">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="278">
+      <c r="BL4" s="280">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7620,6 +7620,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="BJ4:BK4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
     <mergeCell ref="A2:BM2"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
@@ -7636,56 +7686,6 @@
     <mergeCell ref="BF3:BG3"/>
     <mergeCell ref="BH3:BI3"/>
     <mergeCell ref="V4:W4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="BJ4:BK4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7743,7 +7743,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8909,7 +8909,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8923,49 +8923,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1">
-      <c r="A4" s="284" t="s">
+      <c r="A4" s="289" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="284" t="s">
+      <c r="C4" s="289" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="284" t="s">
+      <c r="E4" s="289" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="284" t="s">
+      <c r="G4" s="289" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="284" t="s">
+      <c r="I4" s="289" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1">
-      <c r="A5" s="286" t="str">
+      <c r="A5" s="285" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="285">
+      <c r="C5" s="284">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="288">
+      <c r="E5" s="287">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="287">
+      <c r="G5" s="286">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="289" t="s">
+      <c r="I5" s="288" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9116,11 +9116,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9128,6 +9123,11 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9230,11 +9230,15 @@
       <c r="E4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="F4" s="10">
+        <v>2</v>
+      </c>
+      <c r="G4" s="10">
+        <v>1</v>
+      </c>
       <c r="H4" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -11017,7 +11021,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11169,219 +11173,219 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="256" t="s">
+      <c r="B3" s="263" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="256" t="s">
+      <c r="D3" s="263" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="256" t="s">
+      <c r="F3" s="263" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="256" t="s">
+      <c r="H3" s="263" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="256" t="s">
+      <c r="J3" s="263" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="256" t="s">
+      <c r="L3" s="263" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="260" t="s">
+      <c r="N3" s="264" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="260" t="s">
+      <c r="P3" s="264" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="260" t="s">
+      <c r="R3" s="264" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="260" t="s">
+      <c r="T3" s="264" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="260" t="s">
+      <c r="V3" s="264" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="260" t="s">
+      <c r="X3" s="264" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="261" t="s">
+      <c r="Z3" s="259" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="261" t="s">
+      <c r="AB3" s="259" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="261" t="s">
+      <c r="AD3" s="259" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="261" t="s">
+      <c r="AF3" s="259" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="261" t="s">
+      <c r="AH3" s="259" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="261" t="s">
+      <c r="AJ3" s="259" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="257" t="s">
+      <c r="AL3" s="260" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="257" t="s">
+      <c r="AN3" s="260" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="257" t="s">
+      <c r="AP3" s="260" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="257" t="s">
+      <c r="AR3" s="260" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="257" t="s">
+      <c r="AT3" s="260" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="257" t="s">
+      <c r="AV3" s="260" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="258" t="s">
+      <c r="AX3" s="265" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="258" t="s">
+      <c r="AZ3" s="265" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="258" t="s">
+      <c r="BB3" s="265" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="258" t="s">
+      <c r="BD3" s="265" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="258" t="s">
+      <c r="BF3" s="265" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="258" t="s">
+      <c r="BH3" s="265" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="262" t="s">
+      <c r="BJ3" s="266" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="262" t="s">
+      <c r="BL3" s="266" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="262" t="s">
+      <c r="BN3" s="266" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="262" t="s">
+      <c r="BP3" s="266" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="262" t="s">
+      <c r="BR3" s="266" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="262" t="s">
+      <c r="BT3" s="266" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
-      <c r="BV3" s="263" t="s">
+      <c r="BV3" s="256" t="s">
         <v>224</v>
       </c>
       <c r="BW3" s="253"/>
-      <c r="BX3" s="263" t="s">
+      <c r="BX3" s="256" t="s">
         <v>225</v>
       </c>
       <c r="BY3" s="253"/>
-      <c r="BZ3" s="263" t="s">
+      <c r="BZ3" s="256" t="s">
         <v>226</v>
       </c>
       <c r="CA3" s="253"/>
-      <c r="CB3" s="263" t="s">
+      <c r="CB3" s="256" t="s">
         <v>227</v>
       </c>
       <c r="CC3" s="253"/>
-      <c r="CD3" s="263" t="s">
+      <c r="CD3" s="256" t="s">
         <v>228</v>
       </c>
       <c r="CE3" s="253"/>
-      <c r="CF3" s="263" t="s">
+      <c r="CF3" s="256" t="s">
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="259" t="s">
+      <c r="CH3" s="257" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="259" t="s">
+      <c r="CJ3" s="257" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="259" t="s">
+      <c r="CL3" s="257" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="259" t="s">
+      <c r="CN3" s="257" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="259" t="s">
+      <c r="CP3" s="257" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="259" t="s">
+      <c r="CR3" s="257" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
-      <c r="CT3" s="265" t="s">
+      <c r="CT3" s="258" t="s">
         <v>236</v>
       </c>
       <c r="CU3" s="253"/>
-      <c r="CV3" s="265" t="s">
+      <c r="CV3" s="258" t="s">
         <v>237</v>
       </c>
       <c r="CW3" s="253"/>
-      <c r="CX3" s="265" t="s">
+      <c r="CX3" s="258" t="s">
         <v>238</v>
       </c>
       <c r="CY3" s="253"/>
-      <c r="CZ3" s="265" t="s">
+      <c r="CZ3" s="258" t="s">
         <v>239</v>
       </c>
       <c r="DA3" s="253"/>
-      <c r="DB3" s="265" t="s">
+      <c r="DB3" s="258" t="s">
         <v>240</v>
       </c>
       <c r="DC3" s="253"/>
-      <c r="DD3" s="265" t="s">
+      <c r="DD3" s="258" t="s">
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
@@ -11409,51 +11413,51 @@
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="266" t="s">
+      <c r="DR3" s="268" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="266" t="s">
+      <c r="DT3" s="268" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="266" t="s">
+      <c r="DV3" s="268" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="266" t="s">
+      <c r="DX3" s="268" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="266" t="s">
+      <c r="DZ3" s="268" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="266" t="s">
+      <c r="EB3" s="268" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="264" t="s">
+      <c r="ED3" s="262" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="264" t="s">
+      <c r="EF3" s="262" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="264" t="s">
+      <c r="EH3" s="262" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="264" t="s">
+      <c r="EJ3" s="262" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="264" t="s">
+      <c r="EL3" s="262" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="264" t="s">
+      <c r="EN3" s="262" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12493,16 +12497,54 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="CJ3:CK3"/>
+    <mergeCell ref="CL3:CM3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="BT3:BU3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="CF3:CG3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="DN3:DO3"/>
+    <mergeCell ref="A1:EO1"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="CR3:CS3"/>
     <mergeCell ref="A2:EO2"/>
     <mergeCell ref="EJ3:EK3"/>
     <mergeCell ref="D3:E3"/>
@@ -12519,54 +12561,16 @@
     <mergeCell ref="DJ3:DK3"/>
     <mergeCell ref="EL3:EM3"/>
     <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="A1:EO1"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="CJ3:CK3"/>
-    <mergeCell ref="CL3:CM3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="BT3:BU3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="CF3:CG3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="CT3:CU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12592,7 +12596,7 @@
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12745,7 +12749,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>
@@ -13276,9 +13280,9 @@
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B5="",'Apostas - Grupos'!C5=""),0,IF(AND('Apostas - Grupos'!B5='Jogos - Grupos'!F3,'Apostas - Grupos'!C5='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B5='Apostas - Grupos'!C5),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B5&gt;'Apostas - Grupos'!C5),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B5&lt;'Apostas - Grupos'!C5)),IF(('Apostas - Grupos'!B5-'Apostas - Grupos'!C5)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="C5" s="106" t="str">
+      <c r="C5" s="106">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D5="",'Apostas - Grupos'!E5=""),0,IF(AND('Apostas - Grupos'!D5='Jogos - Grupos'!F4,'Apostas - Grupos'!E5='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D5='Apostas - Grupos'!E5),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D5&gt;'Apostas - Grupos'!E5),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D5&lt;'Apostas - Grupos'!E5)),IF(('Apostas - Grupos'!D5-'Apostas - Grupos'!E5)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="D5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F5="",'Apostas - Grupos'!G5=""),0,IF(AND('Apostas - Grupos'!F5='Jogos - Grupos'!F5,'Apostas - Grupos'!G5='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F5='Apostas - Grupos'!G5),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F5&gt;'Apostas - Grupos'!G5),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F5&lt;'Apostas - Grupos'!G5)),IF(('Apostas - Grupos'!F5-'Apostas - Grupos'!G5)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13573,9 +13577,9 @@
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B6="",'Apostas - Grupos'!C6=""),0,IF(AND('Apostas - Grupos'!B6='Jogos - Grupos'!F3,'Apostas - Grupos'!C6='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B6='Apostas - Grupos'!C6),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B6&gt;'Apostas - Grupos'!C6),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B6&lt;'Apostas - Grupos'!C6)),IF(('Apostas - Grupos'!B6-'Apostas - Grupos'!C6)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="C6" s="108" t="str">
+      <c r="C6" s="108">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D6="",'Apostas - Grupos'!E6=""),0,IF(AND('Apostas - Grupos'!D6='Jogos - Grupos'!F4,'Apostas - Grupos'!E6='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D6='Apostas - Grupos'!E6),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D6&gt;'Apostas - Grupos'!E6),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D6&lt;'Apostas - Grupos'!E6)),IF(('Apostas - Grupos'!D6-'Apostas - Grupos'!E6)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="D6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F6="",'Apostas - Grupos'!G6=""),0,IF(AND('Apostas - Grupos'!F6='Jogos - Grupos'!F5,'Apostas - Grupos'!G6='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F6='Apostas - Grupos'!G6),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F6&gt;'Apostas - Grupos'!G6),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F6&lt;'Apostas - Grupos'!G6)),IF(('Apostas - Grupos'!F6-'Apostas - Grupos'!G6)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13870,9 +13874,9 @@
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B7="",'Apostas - Grupos'!C7=""),0,IF(AND('Apostas - Grupos'!B7='Jogos - Grupos'!F3,'Apostas - Grupos'!C7='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B7='Apostas - Grupos'!C7),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B7&gt;'Apostas - Grupos'!C7),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B7&lt;'Apostas - Grupos'!C7)),IF(('Apostas - Grupos'!B7-'Apostas - Grupos'!C7)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="C7" s="106" t="str">
+      <c r="C7" s="106">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D7="",'Apostas - Grupos'!E7=""),0,IF(AND('Apostas - Grupos'!D7='Jogos - Grupos'!F4,'Apostas - Grupos'!E7='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D7='Apostas - Grupos'!E7),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D7&gt;'Apostas - Grupos'!E7),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D7&lt;'Apostas - Grupos'!E7)),IF(('Apostas - Grupos'!D7-'Apostas - Grupos'!E7)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="D7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F7="",'Apostas - Grupos'!G7=""),0,IF(AND('Apostas - Grupos'!F7='Jogos - Grupos'!F5,'Apostas - Grupos'!G7='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F7='Apostas - Grupos'!G7),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F7&gt;'Apostas - Grupos'!G7),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F7&lt;'Apostas - Grupos'!G7)),IF(('Apostas - Grupos'!F7-'Apostas - Grupos'!G7)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -14167,9 +14171,9 @@
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B8="",'Apostas - Grupos'!C8=""),0,IF(AND('Apostas - Grupos'!B8='Jogos - Grupos'!F3,'Apostas - Grupos'!C8='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B8='Apostas - Grupos'!C8),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B8&gt;'Apostas - Grupos'!C8),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B8&lt;'Apostas - Grupos'!C8)),IF(('Apostas - Grupos'!B8-'Apostas - Grupos'!C8)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="C8" s="108" t="str">
+      <c r="C8" s="108">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D8="",'Apostas - Grupos'!E8=""),0,IF(AND('Apostas - Grupos'!D8='Jogos - Grupos'!F4,'Apostas - Grupos'!E8='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D8='Apostas - Grupos'!E8),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D8&gt;'Apostas - Grupos'!E8),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D8&lt;'Apostas - Grupos'!E8)),IF(('Apostas - Grupos'!D8-'Apostas - Grupos'!E8)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="D8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F8="",'Apostas - Grupos'!G8=""),0,IF(AND('Apostas - Grupos'!F8='Jogos - Grupos'!F5,'Apostas - Grupos'!G8='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F8='Apostas - Grupos'!G8),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F8&gt;'Apostas - Grupos'!G8),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F8&lt;'Apostas - Grupos'!G8)),IF(('Apostas - Grupos'!F8-'Apostas - Grupos'!G8)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -14643,7 +14647,7 @@
       </c>
       <c r="C5" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$D$3:$D$74=$B5)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$E$3:$E$74=$B5)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*(('Jogos - Grupos'!$D$3:$D$74=$B5)+('Jogos - Grupos'!$E$3:$E$74=$B5))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14651,23 +14655,23 @@
       </c>
       <c r="E5" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$D$3:$D$74=$B5)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$E$3:$E$74=$B5)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$D$3:$D$74=$B5)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$E$3:$E$74=$B5)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="110">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" s="110">
         <f t="shared" si="2"/>
-        <v>200000477</v>
+        <v>3201002477</v>
       </c>
       <c r="J5" s="8">
         <f>RANK(I5,$I$3:$I$6,0)</f>
@@ -14694,15 +14698,15 @@
       </c>
       <c r="E6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="110">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="1"/>
@@ -14710,7 +14714,7 @@
       </c>
       <c r="I6" s="110">
         <f t="shared" si="2"/>
-        <v>200000462</v>
+        <v>199001462</v>
       </c>
       <c r="J6" s="8">
         <f>RANK(I6,$I$3:$I$6,0)</f>
@@ -16905,11 +16909,11 @@
       </c>
       <c r="C68" s="149">
         <f>IFERROR(INDEX($I$3:$I$6,MATCH(3,$J$3:$J$6,0)),0)</f>
-        <v>200000462</v>
+        <v>199001462</v>
       </c>
       <c r="D68" s="150">
         <f t="shared" ref="D68:D79" si="3">RANK(C68,$C$68:$C$79,0)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -16926,7 +16930,7 @@
       </c>
       <c r="D69" s="150">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -16977,7 +16981,7 @@
       </c>
       <c r="D72" s="150">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -17028,7 +17032,7 @@
       </c>
       <c r="D75" s="150">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -17079,7 +17083,7 @@
       </c>
       <c r="D78" s="150">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -17096,7 +17100,7 @@
       </c>
       <c r="D79" s="150">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -17167,7 +17171,7 @@
       </c>
       <c r="B88" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(7,$D$68:$D$79,0)),"?")</f>
-        <v>Tchequia</v>
+        <v>Costa do Marfim</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -17176,7 +17180,7 @@
       </c>
       <c r="B89" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(8,$D$68:$D$79,0)),"?")</f>
-        <v>Costa do Marfim</v>
+        <v>Canada</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -17185,7 +17189,7 @@
       </c>
       <c r="B92" s="166" t="str">
         <f>IF(D68&lt;=8,"A","")&amp;IF(D69&lt;=8,"B","")&amp;IF(D70&lt;=8,"C","")&amp;IF(D71&lt;=8,"D","")&amp;IF(D72&lt;=8,"E","")&amp;IF(D73&lt;=8,"F","")&amp;IF(D74&lt;=8,"G","")&amp;IF(D75&lt;=8,"H","")&amp;IF(D76&lt;=8,"I","")&amp;IF(D77&lt;=8,"J","")&amp;IF(D78&lt;=8,"K","")&amp;IF(D79&lt;=8,"L","")</f>
-        <v>ACDEFGIJ</v>
+        <v>BCDEFGIJ</v>
       </c>
     </row>
   </sheetData>
@@ -43938,7 +43942,7 @@
       </c>
       <c r="E12" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,4,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Argelia</v>
+        <v>Canada</v>
       </c>
       <c r="F12" s="249"/>
       <c r="G12" s="249"/>
@@ -43968,7 +43972,7 @@
       </c>
       <c r="E13" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,6,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Tchequia</v>
+        <v>Argelia</v>
       </c>
       <c r="F13" s="249"/>
       <c r="G13" s="249"/>

--- a/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\projetos\bolão_copa\gabarito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8974CD40-D127-45CF-847C-8731A5330C22}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7643D37-11D7-4CF6-8522-293204FDA553}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4976,73 +4976,67 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5051,13 +5045,22 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5073,9 +5076,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5836,7 +5836,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5972,67 +5972,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="270" t="s">
+      <c r="AH3" s="273" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="270" t="s">
+      <c r="AJ3" s="273" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="270" t="s">
+      <c r="AL3" s="273" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="270" t="s">
+      <c r="AN3" s="273" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="270" t="s">
+      <c r="AP3" s="273" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="270" t="s">
+      <c r="AR3" s="273" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="270" t="s">
+      <c r="AT3" s="273" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="270" t="s">
+      <c r="AV3" s="273" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="274" t="s">
+      <c r="AX3" s="275" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="274" t="s">
+      <c r="AZ3" s="275" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="274" t="s">
+      <c r="BB3" s="275" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="274" t="s">
+      <c r="BD3" s="275" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="277" t="s">
+      <c r="BF3" s="281" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="277" t="s">
+      <c r="BH3" s="281" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="273" t="s">
+      <c r="BJ3" s="279" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="275" t="s">
+      <c r="BL3" s="280" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -6041,131 +6041,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="272">
+      <c r="B4" s="270">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="272">
+      <c r="D4" s="270">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="272">
+      <c r="F4" s="270">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="272">
+      <c r="H4" s="270">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="272">
+      <c r="J4" s="270">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="272">
+      <c r="L4" s="270">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="272">
+      <c r="N4" s="270">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="272">
+      <c r="P4" s="270">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="272">
+      <c r="R4" s="270">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="272">
+      <c r="T4" s="270">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="272">
+      <c r="V4" s="270">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="272">
+      <c r="X4" s="270">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="272">
+      <c r="Z4" s="270">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="272">
+      <c r="AB4" s="270">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="272">
+      <c r="AD4" s="270">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="272">
+      <c r="AF4" s="270">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="276">
+      <c r="AH4" s="274">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="276">
+      <c r="AJ4" s="274">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="276">
+      <c r="AL4" s="274">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="276">
+      <c r="AN4" s="274">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="276">
+      <c r="AP4" s="274">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="276">
+      <c r="AR4" s="274">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="276">
+      <c r="AT4" s="274">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="276">
+      <c r="AV4" s="274">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="278">
+      <c r="AX4" s="272">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="278">
+      <c r="AZ4" s="272">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="278">
+      <c r="BB4" s="272">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="278">
+      <c r="BD4" s="272">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="279">
+      <c r="BF4" s="277">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="279">
+      <c r="BH4" s="277">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="281">
+      <c r="BJ4" s="276">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="280">
+      <c r="BL4" s="278">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7620,19 +7620,43 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="A2:BM2"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
@@ -7649,43 +7673,19 @@
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="AV3:AW3"/>
     <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="A2:BM2"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7743,7 +7743,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8909,7 +8909,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8923,49 +8923,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1">
-      <c r="A4" s="289" t="s">
+      <c r="A4" s="284" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="289" t="s">
+      <c r="C4" s="284" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="289" t="s">
+      <c r="E4" s="284" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="289" t="s">
+      <c r="G4" s="284" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="289" t="s">
+      <c r="I4" s="284" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1">
-      <c r="A5" s="285" t="str">
+      <c r="A5" s="286" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="284">
+      <c r="C5" s="285">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="287">
+      <c r="E5" s="288">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
         <v>4</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="286">
+      <c r="G5" s="287">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="288" t="s">
+      <c r="I5" s="289" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9116,6 +9116,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9123,11 +9128,6 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11029,7 +11029,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11181,219 +11181,219 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="263" t="s">
+      <c r="B3" s="256" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="263" t="s">
+      <c r="D3" s="256" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="263" t="s">
+      <c r="F3" s="256" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="263" t="s">
+      <c r="H3" s="256" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="263" t="s">
+      <c r="J3" s="256" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="263" t="s">
+      <c r="L3" s="256" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="264" t="s">
+      <c r="N3" s="260" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="264" t="s">
+      <c r="P3" s="260" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="264" t="s">
+      <c r="R3" s="260" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="260" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="264" t="s">
+      <c r="V3" s="260" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="264" t="s">
+      <c r="X3" s="260" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="259" t="s">
+      <c r="Z3" s="261" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="259" t="s">
+      <c r="AB3" s="261" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="259" t="s">
+      <c r="AD3" s="261" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="259" t="s">
+      <c r="AF3" s="261" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="259" t="s">
+      <c r="AH3" s="261" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="259" t="s">
+      <c r="AJ3" s="261" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="260" t="s">
+      <c r="AL3" s="257" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="260" t="s">
+      <c r="AN3" s="257" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="260" t="s">
+      <c r="AP3" s="257" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="260" t="s">
+      <c r="AR3" s="257" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="260" t="s">
+      <c r="AT3" s="257" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="260" t="s">
+      <c r="AV3" s="257" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="265" t="s">
+      <c r="AX3" s="258" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="265" t="s">
+      <c r="AZ3" s="258" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="265" t="s">
+      <c r="BB3" s="258" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="265" t="s">
+      <c r="BD3" s="258" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="265" t="s">
+      <c r="BF3" s="258" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="265" t="s">
+      <c r="BH3" s="258" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="266" t="s">
+      <c r="BJ3" s="262" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="266" t="s">
+      <c r="BL3" s="262" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="266" t="s">
+      <c r="BN3" s="262" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="266" t="s">
+      <c r="BP3" s="262" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="266" t="s">
+      <c r="BR3" s="262" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="266" t="s">
+      <c r="BT3" s="262" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
-      <c r="BV3" s="256" t="s">
+      <c r="BV3" s="263" t="s">
         <v>224</v>
       </c>
       <c r="BW3" s="253"/>
-      <c r="BX3" s="256" t="s">
+      <c r="BX3" s="263" t="s">
         <v>225</v>
       </c>
       <c r="BY3" s="253"/>
-      <c r="BZ3" s="256" t="s">
+      <c r="BZ3" s="263" t="s">
         <v>226</v>
       </c>
       <c r="CA3" s="253"/>
-      <c r="CB3" s="256" t="s">
+      <c r="CB3" s="263" t="s">
         <v>227</v>
       </c>
       <c r="CC3" s="253"/>
-      <c r="CD3" s="256" t="s">
+      <c r="CD3" s="263" t="s">
         <v>228</v>
       </c>
       <c r="CE3" s="253"/>
-      <c r="CF3" s="256" t="s">
+      <c r="CF3" s="263" t="s">
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="257" t="s">
+      <c r="CH3" s="259" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="257" t="s">
+      <c r="CJ3" s="259" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="257" t="s">
+      <c r="CL3" s="259" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="257" t="s">
+      <c r="CN3" s="259" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="257" t="s">
+      <c r="CP3" s="259" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="257" t="s">
+      <c r="CR3" s="259" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
-      <c r="CT3" s="258" t="s">
+      <c r="CT3" s="265" t="s">
         <v>236</v>
       </c>
       <c r="CU3" s="253"/>
-      <c r="CV3" s="258" t="s">
+      <c r="CV3" s="265" t="s">
         <v>237</v>
       </c>
       <c r="CW3" s="253"/>
-      <c r="CX3" s="258" t="s">
+      <c r="CX3" s="265" t="s">
         <v>238</v>
       </c>
       <c r="CY3" s="253"/>
-      <c r="CZ3" s="258" t="s">
+      <c r="CZ3" s="265" t="s">
         <v>239</v>
       </c>
       <c r="DA3" s="253"/>
-      <c r="DB3" s="258" t="s">
+      <c r="DB3" s="265" t="s">
         <v>240</v>
       </c>
       <c r="DC3" s="253"/>
-      <c r="DD3" s="258" t="s">
+      <c r="DD3" s="265" t="s">
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
@@ -11421,51 +11421,51 @@
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="268" t="s">
+      <c r="DR3" s="266" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="268" t="s">
+      <c r="DT3" s="266" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="268" t="s">
+      <c r="DV3" s="266" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="268" t="s">
+      <c r="DX3" s="266" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="268" t="s">
+      <c r="DZ3" s="266" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="268" t="s">
+      <c r="EB3" s="266" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="262" t="s">
+      <c r="ED3" s="264" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="262" t="s">
+      <c r="EF3" s="264" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="262" t="s">
+      <c r="EH3" s="264" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="262" t="s">
+      <c r="EJ3" s="264" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="262" t="s">
+      <c r="EL3" s="264" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="262" t="s">
+      <c r="EN3" s="264" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12505,6 +12505,64 @@
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="A2:EO2"/>
+    <mergeCell ref="EJ3:EK3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="DL3:DM3"/>
+    <mergeCell ref="BV3:BW3"/>
+    <mergeCell ref="CB3:CC3"/>
+    <mergeCell ref="DJ3:DK3"/>
+    <mergeCell ref="EL3:EM3"/>
+    <mergeCell ref="CV3:CW3"/>
+    <mergeCell ref="A1:EO1"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="CR3:CS3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="DN3:DO3"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
@@ -12521,64 +12579,6 @@
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="A1:EO1"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="A2:EO2"/>
-    <mergeCell ref="EJ3:EK3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="DL3:DM3"/>
-    <mergeCell ref="BV3:BW3"/>
-    <mergeCell ref="CB3:CC3"/>
-    <mergeCell ref="DJ3:DK3"/>
-    <mergeCell ref="EL3:EM3"/>
-    <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="CT3:CU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12604,7 +12604,7 @@
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12757,7 +12757,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>

--- a/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\projetos\bolão_copa\gabarito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7643D37-11D7-4CF6-8522-293204FDA553}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D2E588-B5BD-4DF0-9736-CE9B2961CC1C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regras" sheetId="1" r:id="rId1"/>
@@ -4976,67 +4976,73 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5045,22 +5051,13 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5076,6 +5073,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5836,7 +5836,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5972,67 +5972,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="273" t="s">
+      <c r="AH3" s="270" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="273" t="s">
+      <c r="AJ3" s="270" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="273" t="s">
+      <c r="AL3" s="270" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="273" t="s">
+      <c r="AN3" s="270" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="273" t="s">
+      <c r="AP3" s="270" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="273" t="s">
+      <c r="AR3" s="270" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="273" t="s">
+      <c r="AT3" s="270" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="273" t="s">
+      <c r="AV3" s="270" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="275" t="s">
+      <c r="AX3" s="274" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="275" t="s">
+      <c r="AZ3" s="274" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="275" t="s">
+      <c r="BB3" s="274" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="275" t="s">
+      <c r="BD3" s="274" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="281" t="s">
+      <c r="BF3" s="277" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="281" t="s">
+      <c r="BH3" s="277" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="279" t="s">
+      <c r="BJ3" s="273" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="280" t="s">
+      <c r="BL3" s="275" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -6041,131 +6041,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="270">
+      <c r="B4" s="272">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="270">
+      <c r="D4" s="272">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="270">
+      <c r="F4" s="272">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="270">
+      <c r="H4" s="272">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="270">
+      <c r="J4" s="272">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="270">
+      <c r="L4" s="272">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="270">
+      <c r="N4" s="272">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="270">
+      <c r="P4" s="272">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="270">
+      <c r="R4" s="272">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="270">
+      <c r="T4" s="272">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="270">
+      <c r="V4" s="272">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="270">
+      <c r="X4" s="272">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="270">
+      <c r="Z4" s="272">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="270">
+      <c r="AB4" s="272">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="270">
+      <c r="AD4" s="272">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="270">
+      <c r="AF4" s="272">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="274">
+      <c r="AH4" s="276">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="274">
+      <c r="AJ4" s="276">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="274">
+      <c r="AL4" s="276">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="274">
+      <c r="AN4" s="276">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="274">
+      <c r="AP4" s="276">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="274">
+      <c r="AR4" s="276">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="274">
+      <c r="AT4" s="276">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="274">
+      <c r="AV4" s="276">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="272">
+      <c r="AX4" s="278">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="272">
+      <c r="AZ4" s="278">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="272">
+      <c r="BB4" s="278">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="272">
+      <c r="BD4" s="278">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="277">
+      <c r="BF4" s="279">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="277">
+      <c r="BH4" s="279">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="276">
+      <c r="BJ4" s="281">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="278">
+      <c r="BL4" s="280">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7620,6 +7620,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="BJ4:BK4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
     <mergeCell ref="A2:BM2"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
@@ -7636,56 +7686,6 @@
     <mergeCell ref="BF3:BG3"/>
     <mergeCell ref="BH3:BI3"/>
     <mergeCell ref="V4:W4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="BJ4:BK4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7743,7 +7743,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8909,7 +8909,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8923,49 +8923,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1">
-      <c r="A4" s="284" t="s">
+      <c r="A4" s="289" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="284" t="s">
+      <c r="C4" s="289" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="284" t="s">
+      <c r="E4" s="289" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="284" t="s">
+      <c r="G4" s="289" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="284" t="s">
+      <c r="I4" s="289" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1">
-      <c r="A5" s="286" t="str">
+      <c r="A5" s="285" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="285">
+      <c r="C5" s="284">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="288">
+      <c r="E5" s="287">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="287">
+      <c r="G5" s="286">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="289" t="s">
+      <c r="I5" s="288" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9116,11 +9116,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9128,6 +9123,11 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9376,11 +9376,15 @@
       <c r="E10" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
       <c r="H10" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -11029,7 +11033,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11181,219 +11185,219 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="256" t="s">
+      <c r="B3" s="263" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="256" t="s">
+      <c r="D3" s="263" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="256" t="s">
+      <c r="F3" s="263" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="256" t="s">
+      <c r="H3" s="263" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="256" t="s">
+      <c r="J3" s="263" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="256" t="s">
+      <c r="L3" s="263" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="260" t="s">
+      <c r="N3" s="264" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="260" t="s">
+      <c r="P3" s="264" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="260" t="s">
+      <c r="R3" s="264" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="260" t="s">
+      <c r="T3" s="264" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="260" t="s">
+      <c r="V3" s="264" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="260" t="s">
+      <c r="X3" s="264" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="261" t="s">
+      <c r="Z3" s="259" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="261" t="s">
+      <c r="AB3" s="259" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="261" t="s">
+      <c r="AD3" s="259" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="261" t="s">
+      <c r="AF3" s="259" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="261" t="s">
+      <c r="AH3" s="259" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="261" t="s">
+      <c r="AJ3" s="259" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="257" t="s">
+      <c r="AL3" s="260" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="257" t="s">
+      <c r="AN3" s="260" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="257" t="s">
+      <c r="AP3" s="260" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="257" t="s">
+      <c r="AR3" s="260" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="257" t="s">
+      <c r="AT3" s="260" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="257" t="s">
+      <c r="AV3" s="260" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="258" t="s">
+      <c r="AX3" s="265" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="258" t="s">
+      <c r="AZ3" s="265" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="258" t="s">
+      <c r="BB3" s="265" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="258" t="s">
+      <c r="BD3" s="265" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="258" t="s">
+      <c r="BF3" s="265" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="258" t="s">
+      <c r="BH3" s="265" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="262" t="s">
+      <c r="BJ3" s="266" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="262" t="s">
+      <c r="BL3" s="266" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="262" t="s">
+      <c r="BN3" s="266" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="262" t="s">
+      <c r="BP3" s="266" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="262" t="s">
+      <c r="BR3" s="266" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="262" t="s">
+      <c r="BT3" s="266" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
-      <c r="BV3" s="263" t="s">
+      <c r="BV3" s="256" t="s">
         <v>224</v>
       </c>
       <c r="BW3" s="253"/>
-      <c r="BX3" s="263" t="s">
+      <c r="BX3" s="256" t="s">
         <v>225</v>
       </c>
       <c r="BY3" s="253"/>
-      <c r="BZ3" s="263" t="s">
+      <c r="BZ3" s="256" t="s">
         <v>226</v>
       </c>
       <c r="CA3" s="253"/>
-      <c r="CB3" s="263" t="s">
+      <c r="CB3" s="256" t="s">
         <v>227</v>
       </c>
       <c r="CC3" s="253"/>
-      <c r="CD3" s="263" t="s">
+      <c r="CD3" s="256" t="s">
         <v>228</v>
       </c>
       <c r="CE3" s="253"/>
-      <c r="CF3" s="263" t="s">
+      <c r="CF3" s="256" t="s">
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="259" t="s">
+      <c r="CH3" s="257" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="259" t="s">
+      <c r="CJ3" s="257" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="259" t="s">
+      <c r="CL3" s="257" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="259" t="s">
+      <c r="CN3" s="257" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="259" t="s">
+      <c r="CP3" s="257" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="259" t="s">
+      <c r="CR3" s="257" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
-      <c r="CT3" s="265" t="s">
+      <c r="CT3" s="258" t="s">
         <v>236</v>
       </c>
       <c r="CU3" s="253"/>
-      <c r="CV3" s="265" t="s">
+      <c r="CV3" s="258" t="s">
         <v>237</v>
       </c>
       <c r="CW3" s="253"/>
-      <c r="CX3" s="265" t="s">
+      <c r="CX3" s="258" t="s">
         <v>238</v>
       </c>
       <c r="CY3" s="253"/>
-      <c r="CZ3" s="265" t="s">
+      <c r="CZ3" s="258" t="s">
         <v>239</v>
       </c>
       <c r="DA3" s="253"/>
-      <c r="DB3" s="265" t="s">
+      <c r="DB3" s="258" t="s">
         <v>240</v>
       </c>
       <c r="DC3" s="253"/>
-      <c r="DD3" s="265" t="s">
+      <c r="DD3" s="258" t="s">
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
@@ -11421,51 +11425,51 @@
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="266" t="s">
+      <c r="DR3" s="268" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="266" t="s">
+      <c r="DT3" s="268" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="266" t="s">
+      <c r="DV3" s="268" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="266" t="s">
+      <c r="DX3" s="268" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="266" t="s">
+      <c r="DZ3" s="268" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="266" t="s">
+      <c r="EB3" s="268" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="264" t="s">
+      <c r="ED3" s="262" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="264" t="s">
+      <c r="EF3" s="262" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="264" t="s">
+      <c r="EH3" s="262" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="264" t="s">
+      <c r="EJ3" s="262" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="264" t="s">
+      <c r="EL3" s="262" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="264" t="s">
+      <c r="EN3" s="262" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12505,16 +12509,54 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="CJ3:CK3"/>
+    <mergeCell ref="CL3:CM3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="BT3:BU3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="CF3:CG3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="DN3:DO3"/>
+    <mergeCell ref="A1:EO1"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="CR3:CS3"/>
     <mergeCell ref="A2:EO2"/>
     <mergeCell ref="EJ3:EK3"/>
     <mergeCell ref="D3:E3"/>
@@ -12531,54 +12573,16 @@
     <mergeCell ref="DJ3:DK3"/>
     <mergeCell ref="EL3:EM3"/>
     <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="A1:EO1"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="CJ3:CK3"/>
-    <mergeCell ref="CL3:CM3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="BT3:BU3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="CF3:CG3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="CT3:CU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12604,7 +12608,7 @@
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12757,7 +12761,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>
@@ -13312,9 +13316,9 @@
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N5="",'Apostas - Grupos'!O5=""),0,IF(AND('Apostas - Grupos'!N5='Jogos - Grupos'!F9,'Apostas - Grupos'!O5='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N5='Apostas - Grupos'!O5),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N5&gt;'Apostas - Grupos'!O5),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N5&lt;'Apostas - Grupos'!O5)),IF(('Apostas - Grupos'!N5-'Apostas - Grupos'!O5)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="I5" s="106" t="str">
+      <c r="I5" s="106">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P5="",'Apostas - Grupos'!Q5=""),0,IF(AND('Apostas - Grupos'!P5='Jogos - Grupos'!F10,'Apostas - Grupos'!Q5='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P5='Apostas - Grupos'!Q5),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P5&gt;'Apostas - Grupos'!Q5),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P5&lt;'Apostas - Grupos'!Q5)),IF(('Apostas - Grupos'!P5-'Apostas - Grupos'!Q5)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="J5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R5="",'Apostas - Grupos'!S5=""),0,IF(AND('Apostas - Grupos'!R5='Jogos - Grupos'!F11,'Apostas - Grupos'!S5='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R5='Apostas - Grupos'!S5),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R5&gt;'Apostas - Grupos'!S5),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R5&lt;'Apostas - Grupos'!S5)),IF(('Apostas - Grupos'!R5-'Apostas - Grupos'!S5)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -13609,9 +13613,9 @@
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N6="",'Apostas - Grupos'!O6=""),0,IF(AND('Apostas - Grupos'!N6='Jogos - Grupos'!F9,'Apostas - Grupos'!O6='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N6='Apostas - Grupos'!O6),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N6&gt;'Apostas - Grupos'!O6),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N6&lt;'Apostas - Grupos'!O6)),IF(('Apostas - Grupos'!N6-'Apostas - Grupos'!O6)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="I6" s="108" t="str">
+      <c r="I6" s="108">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P6="",'Apostas - Grupos'!Q6=""),0,IF(AND('Apostas - Grupos'!P6='Jogos - Grupos'!F10,'Apostas - Grupos'!Q6='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P6='Apostas - Grupos'!Q6),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P6&gt;'Apostas - Grupos'!Q6),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P6&lt;'Apostas - Grupos'!Q6)),IF(('Apostas - Grupos'!P6-'Apostas - Grupos'!Q6)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="J6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R6="",'Apostas - Grupos'!S6=""),0,IF(AND('Apostas - Grupos'!R6='Jogos - Grupos'!F11,'Apostas - Grupos'!S6='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R6='Apostas - Grupos'!S6),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R6&gt;'Apostas - Grupos'!S6),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R6&lt;'Apostas - Grupos'!S6)),IF(('Apostas - Grupos'!R6-'Apostas - Grupos'!S6)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -13906,9 +13910,9 @@
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N7="",'Apostas - Grupos'!O7=""),0,IF(AND('Apostas - Grupos'!N7='Jogos - Grupos'!F9,'Apostas - Grupos'!O7='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N7='Apostas - Grupos'!O7),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N7&gt;'Apostas - Grupos'!O7),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N7&lt;'Apostas - Grupos'!O7)),IF(('Apostas - Grupos'!N7-'Apostas - Grupos'!O7)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="I7" s="106" t="str">
+      <c r="I7" s="106">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P7="",'Apostas - Grupos'!Q7=""),0,IF(AND('Apostas - Grupos'!P7='Jogos - Grupos'!F10,'Apostas - Grupos'!Q7='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P7='Apostas - Grupos'!Q7),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P7&gt;'Apostas - Grupos'!Q7),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P7&lt;'Apostas - Grupos'!Q7)),IF(('Apostas - Grupos'!P7-'Apostas - Grupos'!Q7)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="J7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R7="",'Apostas - Grupos'!S7=""),0,IF(AND('Apostas - Grupos'!R7='Jogos - Grupos'!F11,'Apostas - Grupos'!S7='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R7='Apostas - Grupos'!S7),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R7&gt;'Apostas - Grupos'!S7),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R7&lt;'Apostas - Grupos'!S7)),IF(('Apostas - Grupos'!R7-'Apostas - Grupos'!S7)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -14203,9 +14207,9 @@
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N8="",'Apostas - Grupos'!O8=""),0,IF(AND('Apostas - Grupos'!N8='Jogos - Grupos'!F9,'Apostas - Grupos'!O8='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N8='Apostas - Grupos'!O8),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N8&gt;'Apostas - Grupos'!O8),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N8&lt;'Apostas - Grupos'!O8)),IF(('Apostas - Grupos'!N8-'Apostas - Grupos'!O8)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="I8" s="108" t="str">
+      <c r="I8" s="108">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P8="",'Apostas - Grupos'!Q8=""),0,IF(AND('Apostas - Grupos'!P8='Jogos - Grupos'!F10,'Apostas - Grupos'!Q8='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P8='Apostas - Grupos'!Q8),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P8&gt;'Apostas - Grupos'!Q8),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P8&lt;'Apostas - Grupos'!Q8)),IF(('Apostas - Grupos'!P8-'Apostas - Grupos'!Q8)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="J8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R8="",'Apostas - Grupos'!S8=""),0,IF(AND('Apostas - Grupos'!R8='Jogos - Grupos'!F11,'Apostas - Grupos'!S8='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R8='Apostas - Grupos'!S8),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R8&gt;'Apostas - Grupos'!S8),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R8&lt;'Apostas - Grupos'!S8)),IF(('Apostas - Grupos'!R8-'Apostas - Grupos'!S8)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -14769,7 +14773,7 @@
       </c>
       <c r="J7" s="14">
         <f>RANK(I7,$I$7:$I$10,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" s="112">
         <v>44</v>
@@ -14812,7 +14816,7 @@
       </c>
       <c r="J8" s="14">
         <f>RANK(I8,$I$7:$I$10,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8" s="112">
         <v>55</v>
@@ -14831,15 +14835,15 @@
       </c>
       <c r="D9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*(('Jogos - Grupos'!$D$3:$D$74=$B9)+('Jogos - Grupos'!$E$3:$E$74=$B9))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$D$3:$D$74=$B9)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$E$3:$E$74=$B9)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$D$3:$D$74=$B9)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$E$3:$E$74=$B9)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="112">
         <f t="shared" si="0"/>
@@ -14847,15 +14851,15 @@
       </c>
       <c r="H9" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="112">
         <f t="shared" si="2"/>
-        <v>200000462</v>
+        <v>1200001462</v>
       </c>
       <c r="J9" s="14">
         <f>RANK(I9,$I$7:$I$10,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K9" s="112">
         <v>38</v>
@@ -14874,15 +14878,15 @@
       </c>
       <c r="D10" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A10)*(('Jogos - Grupos'!$D$3:$D$74=$B10)+('Jogos - Grupos'!$E$3:$E$74=$B10))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A10)*('Jogos - Grupos'!$D$3:$D$74=$B10)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A10)*('Jogos - Grupos'!$E$3:$E$74=$B10)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A10)*('Jogos - Grupos'!$D$3:$D$74=$B10)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A10)*('Jogos - Grupos'!$E$3:$E$74=$B10)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="112">
         <f t="shared" si="0"/>
@@ -14890,15 +14894,15 @@
       </c>
       <c r="H10" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="112">
         <f t="shared" si="2"/>
-        <v>200000480</v>
+        <v>1200001480</v>
       </c>
       <c r="J10" s="14">
         <f>RANK(I10,$I$7:$I$10,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" s="112">
         <v>20</v>
@@ -16668,19 +16672,19 @@
       </c>
       <c r="B54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(1,$J$7:$J$10,0)),"?")</f>
-        <v>Canada</v>
+        <v>Suica</v>
       </c>
       <c r="C54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(2,$J$7:$J$10,0)),"?")</f>
-        <v>Bosnia e Herzegovina</v>
+        <v>Qatar</v>
       </c>
       <c r="D54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(3,$J$7:$J$10,0)),"?")</f>
-        <v>Suica</v>
+        <v>Canada</v>
       </c>
       <c r="E54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(4,$J$7:$J$10,0)),"?")</f>
-        <v>Qatar</v>
+        <v>Bosnia e Herzegovina</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -16930,11 +16934,11 @@
       </c>
       <c r="B69" s="149" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(3,$J$7:$J$10,0)),"?")</f>
-        <v>Suica</v>
+        <v>Canada</v>
       </c>
       <c r="C69" s="149">
         <f>IFERROR(INDEX($I$7:$I$10,MATCH(3,$J$7:$J$10,0)),0)</f>
-        <v>200000480</v>
+        <v>1200001456</v>
       </c>
       <c r="D69" s="150">
         <f t="shared" si="3"/>
@@ -17125,7 +17129,7 @@
       </c>
       <c r="B82" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(1,$D$68:$D$79,0)),"?")</f>
-        <v>Suica</v>
+        <v>Canada</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -43710,7 +43714,7 @@
       </c>
       <c r="E4" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C54,"Aguardando")</f>
-        <v>Bosnia e Herzegovina</v>
+        <v>Qatar</v>
       </c>
       <c r="F4" s="249"/>
       <c r="G4" s="249"/>
@@ -43950,7 +43954,7 @@
       </c>
       <c r="E12" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,4,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Suica</v>
+        <v>Canada</v>
       </c>
       <c r="F12" s="249"/>
       <c r="G12" s="249"/>
@@ -44066,7 +44070,7 @@
       </c>
       <c r="D16" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!B54,"Aguardando")</f>
-        <v>Canada</v>
+        <v>Suica</v>
       </c>
       <c r="E16" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,3,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>

--- a/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\projetos\bolão_copa\gabarito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D2E588-B5BD-4DF0-9736-CE9B2961CC1C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A06A87A-2EC0-4702-87B2-05DEFBAD04F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="3000" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regras" sheetId="1" r:id="rId1"/>
@@ -4976,73 +4976,67 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5051,13 +5045,22 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5073,9 +5076,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5836,7 +5836,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5972,67 +5972,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="270" t="s">
+      <c r="AH3" s="273" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="270" t="s">
+      <c r="AJ3" s="273" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="270" t="s">
+      <c r="AL3" s="273" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="270" t="s">
+      <c r="AN3" s="273" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="270" t="s">
+      <c r="AP3" s="273" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="270" t="s">
+      <c r="AR3" s="273" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="270" t="s">
+      <c r="AT3" s="273" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="270" t="s">
+      <c r="AV3" s="273" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="274" t="s">
+      <c r="AX3" s="275" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="274" t="s">
+      <c r="AZ3" s="275" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="274" t="s">
+      <c r="BB3" s="275" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="274" t="s">
+      <c r="BD3" s="275" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="277" t="s">
+      <c r="BF3" s="281" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="277" t="s">
+      <c r="BH3" s="281" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="273" t="s">
+      <c r="BJ3" s="279" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="275" t="s">
+      <c r="BL3" s="280" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -6041,131 +6041,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="272">
+      <c r="B4" s="270">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="272">
+      <c r="D4" s="270">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="272">
+      <c r="F4" s="270">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="272">
+      <c r="H4" s="270">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="272">
+      <c r="J4" s="270">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="272">
+      <c r="L4" s="270">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="272">
+      <c r="N4" s="270">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="272">
+      <c r="P4" s="270">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="272">
+      <c r="R4" s="270">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="272">
+      <c r="T4" s="270">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="272">
+      <c r="V4" s="270">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="272">
+      <c r="X4" s="270">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="272">
+      <c r="Z4" s="270">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="272">
+      <c r="AB4" s="270">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="272">
+      <c r="AD4" s="270">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="272">
+      <c r="AF4" s="270">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="276">
+      <c r="AH4" s="274">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="276">
+      <c r="AJ4" s="274">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="276">
+      <c r="AL4" s="274">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="276">
+      <c r="AN4" s="274">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="276">
+      <c r="AP4" s="274">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="276">
+      <c r="AR4" s="274">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="276">
+      <c r="AT4" s="274">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="276">
+      <c r="AV4" s="274">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="278">
+      <c r="AX4" s="272">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="278">
+      <c r="AZ4" s="272">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="278">
+      <c r="BB4" s="272">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="278">
+      <c r="BD4" s="272">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="279">
+      <c r="BF4" s="277">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="279">
+      <c r="BH4" s="277">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="281">
+      <c r="BJ4" s="276">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="280">
+      <c r="BL4" s="278">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7620,19 +7620,43 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="A2:BM2"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
@@ -7649,43 +7673,19 @@
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="AV3:AW3"/>
     <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="A2:BM2"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7743,7 +7743,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8909,7 +8909,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8923,49 +8923,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1">
-      <c r="A4" s="289" t="s">
+      <c r="A4" s="284" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="289" t="s">
+      <c r="C4" s="284" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="289" t="s">
+      <c r="E4" s="284" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="289" t="s">
+      <c r="G4" s="284" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="289" t="s">
+      <c r="I4" s="284" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1">
-      <c r="A5" s="285" t="str">
+      <c r="A5" s="286" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="284">
+      <c r="C5" s="285">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="287">
+      <c r="E5" s="288">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="286">
+      <c r="G5" s="287">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="288" t="s">
+      <c r="I5" s="289" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9116,6 +9116,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9123,11 +9128,6 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9495,11 +9495,15 @@
       <c r="E15" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
+      <c r="F15" s="10">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10">
+        <v>1</v>
+      </c>
       <c r="H15" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -11033,7 +11037,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11185,219 +11189,219 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="263" t="s">
+      <c r="B3" s="256" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="263" t="s">
+      <c r="D3" s="256" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="263" t="s">
+      <c r="F3" s="256" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="263" t="s">
+      <c r="H3" s="256" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="263" t="s">
+      <c r="J3" s="256" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="263" t="s">
+      <c r="L3" s="256" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="264" t="s">
+      <c r="N3" s="260" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="264" t="s">
+      <c r="P3" s="260" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="264" t="s">
+      <c r="R3" s="260" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="260" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="264" t="s">
+      <c r="V3" s="260" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="264" t="s">
+      <c r="X3" s="260" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="259" t="s">
+      <c r="Z3" s="261" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="259" t="s">
+      <c r="AB3" s="261" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="259" t="s">
+      <c r="AD3" s="261" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="259" t="s">
+      <c r="AF3" s="261" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="259" t="s">
+      <c r="AH3" s="261" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="259" t="s">
+      <c r="AJ3" s="261" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="260" t="s">
+      <c r="AL3" s="257" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="260" t="s">
+      <c r="AN3" s="257" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="260" t="s">
+      <c r="AP3" s="257" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="260" t="s">
+      <c r="AR3" s="257" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="260" t="s">
+      <c r="AT3" s="257" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="260" t="s">
+      <c r="AV3" s="257" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="265" t="s">
+      <c r="AX3" s="258" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="265" t="s">
+      <c r="AZ3" s="258" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="265" t="s">
+      <c r="BB3" s="258" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="265" t="s">
+      <c r="BD3" s="258" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="265" t="s">
+      <c r="BF3" s="258" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="265" t="s">
+      <c r="BH3" s="258" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="266" t="s">
+      <c r="BJ3" s="262" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="266" t="s">
+      <c r="BL3" s="262" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="266" t="s">
+      <c r="BN3" s="262" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="266" t="s">
+      <c r="BP3" s="262" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="266" t="s">
+      <c r="BR3" s="262" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="266" t="s">
+      <c r="BT3" s="262" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
-      <c r="BV3" s="256" t="s">
+      <c r="BV3" s="263" t="s">
         <v>224</v>
       </c>
       <c r="BW3" s="253"/>
-      <c r="BX3" s="256" t="s">
+      <c r="BX3" s="263" t="s">
         <v>225</v>
       </c>
       <c r="BY3" s="253"/>
-      <c r="BZ3" s="256" t="s">
+      <c r="BZ3" s="263" t="s">
         <v>226</v>
       </c>
       <c r="CA3" s="253"/>
-      <c r="CB3" s="256" t="s">
+      <c r="CB3" s="263" t="s">
         <v>227</v>
       </c>
       <c r="CC3" s="253"/>
-      <c r="CD3" s="256" t="s">
+      <c r="CD3" s="263" t="s">
         <v>228</v>
       </c>
       <c r="CE3" s="253"/>
-      <c r="CF3" s="256" t="s">
+      <c r="CF3" s="263" t="s">
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="257" t="s">
+      <c r="CH3" s="259" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="257" t="s">
+      <c r="CJ3" s="259" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="257" t="s">
+      <c r="CL3" s="259" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="257" t="s">
+      <c r="CN3" s="259" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="257" t="s">
+      <c r="CP3" s="259" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="257" t="s">
+      <c r="CR3" s="259" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
-      <c r="CT3" s="258" t="s">
+      <c r="CT3" s="265" t="s">
         <v>236</v>
       </c>
       <c r="CU3" s="253"/>
-      <c r="CV3" s="258" t="s">
+      <c r="CV3" s="265" t="s">
         <v>237</v>
       </c>
       <c r="CW3" s="253"/>
-      <c r="CX3" s="258" t="s">
+      <c r="CX3" s="265" t="s">
         <v>238</v>
       </c>
       <c r="CY3" s="253"/>
-      <c r="CZ3" s="258" t="s">
+      <c r="CZ3" s="265" t="s">
         <v>239</v>
       </c>
       <c r="DA3" s="253"/>
-      <c r="DB3" s="258" t="s">
+      <c r="DB3" s="265" t="s">
         <v>240</v>
       </c>
       <c r="DC3" s="253"/>
-      <c r="DD3" s="258" t="s">
+      <c r="DD3" s="265" t="s">
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
@@ -11425,51 +11429,51 @@
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="268" t="s">
+      <c r="DR3" s="266" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="268" t="s">
+      <c r="DT3" s="266" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="268" t="s">
+      <c r="DV3" s="266" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="268" t="s">
+      <c r="DX3" s="266" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="268" t="s">
+      <c r="DZ3" s="266" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="268" t="s">
+      <c r="EB3" s="266" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="262" t="s">
+      <c r="ED3" s="264" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="262" t="s">
+      <c r="EF3" s="264" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="262" t="s">
+      <c r="EH3" s="264" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="262" t="s">
+      <c r="EJ3" s="264" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="262" t="s">
+      <c r="EL3" s="264" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="262" t="s">
+      <c r="EN3" s="264" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12509,6 +12513,64 @@
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="A2:EO2"/>
+    <mergeCell ref="EJ3:EK3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="DL3:DM3"/>
+    <mergeCell ref="BV3:BW3"/>
+    <mergeCell ref="CB3:CC3"/>
+    <mergeCell ref="DJ3:DK3"/>
+    <mergeCell ref="EL3:EM3"/>
+    <mergeCell ref="CV3:CW3"/>
+    <mergeCell ref="A1:EO1"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="CR3:CS3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="DN3:DO3"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
@@ -12525,64 +12587,6 @@
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="A1:EO1"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="A2:EO2"/>
-    <mergeCell ref="EJ3:EK3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="DL3:DM3"/>
-    <mergeCell ref="BV3:BW3"/>
-    <mergeCell ref="CB3:CC3"/>
-    <mergeCell ref="DJ3:DK3"/>
-    <mergeCell ref="EL3:EM3"/>
-    <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="CT3:CU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12608,7 +12612,7 @@
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12761,7 +12765,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>
@@ -13336,9 +13340,9 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X5="",'Apostas - Grupos'!Y5=""),0,IF(AND('Apostas - Grupos'!X5='Jogos - Grupos'!F14,'Apostas - Grupos'!Y5='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X5='Apostas - Grupos'!Y5),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X5&gt;'Apostas - Grupos'!Y5),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X5&lt;'Apostas - Grupos'!Y5)),IF(('Apostas - Grupos'!X5-'Apostas - Grupos'!Y5)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N5" s="106" t="str">
+      <c r="N5" s="106">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z5="",'Apostas - Grupos'!AA5=""),0,IF(AND('Apostas - Grupos'!Z5='Jogos - Grupos'!F15,'Apostas - Grupos'!AA5='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z5='Apostas - Grupos'!AA5),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z5&gt;'Apostas - Grupos'!AA5),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z5&lt;'Apostas - Grupos'!AA5)),IF(('Apostas - Grupos'!Z5-'Apostas - Grupos'!AA5)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="O5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB5="",'Apostas - Grupos'!AC5=""),0,IF(AND('Apostas - Grupos'!AB5='Jogos - Grupos'!F16,'Apostas - Grupos'!AC5='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB5='Apostas - Grupos'!AC5),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB5&gt;'Apostas - Grupos'!AC5),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB5&lt;'Apostas - Grupos'!AC5)),IF(('Apostas - Grupos'!AB5-'Apostas - Grupos'!AC5)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
@@ -13633,9 +13637,9 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X6="",'Apostas - Grupos'!Y6=""),0,IF(AND('Apostas - Grupos'!X6='Jogos - Grupos'!F14,'Apostas - Grupos'!Y6='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X6='Apostas - Grupos'!Y6),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X6&gt;'Apostas - Grupos'!Y6),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X6&lt;'Apostas - Grupos'!Y6)),IF(('Apostas - Grupos'!X6-'Apostas - Grupos'!Y6)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N6" s="108" t="str">
+      <c r="N6" s="108">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z6="",'Apostas - Grupos'!AA6=""),0,IF(AND('Apostas - Grupos'!Z6='Jogos - Grupos'!F15,'Apostas - Grupos'!AA6='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z6='Apostas - Grupos'!AA6),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z6&gt;'Apostas - Grupos'!AA6),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z6&lt;'Apostas - Grupos'!AA6)),IF(('Apostas - Grupos'!Z6-'Apostas - Grupos'!AA6)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="O6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB6="",'Apostas - Grupos'!AC6=""),0,IF(AND('Apostas - Grupos'!AB6='Jogos - Grupos'!F16,'Apostas - Grupos'!AC6='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB6='Apostas - Grupos'!AC6),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB6&gt;'Apostas - Grupos'!AC6),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB6&lt;'Apostas - Grupos'!AC6)),IF(('Apostas - Grupos'!AB6-'Apostas - Grupos'!AC6)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
@@ -13930,9 +13934,9 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X7="",'Apostas - Grupos'!Y7=""),0,IF(AND('Apostas - Grupos'!X7='Jogos - Grupos'!F14,'Apostas - Grupos'!Y7='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X7='Apostas - Grupos'!Y7),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X7&gt;'Apostas - Grupos'!Y7),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X7&lt;'Apostas - Grupos'!Y7)),IF(('Apostas - Grupos'!X7-'Apostas - Grupos'!Y7)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N7" s="106" t="str">
+      <c r="N7" s="106">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z7="",'Apostas - Grupos'!AA7=""),0,IF(AND('Apostas - Grupos'!Z7='Jogos - Grupos'!F15,'Apostas - Grupos'!AA7='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z7='Apostas - Grupos'!AA7),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z7&gt;'Apostas - Grupos'!AA7),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z7&lt;'Apostas - Grupos'!AA7)),IF(('Apostas - Grupos'!Z7-'Apostas - Grupos'!AA7)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="O7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB7="",'Apostas - Grupos'!AC7=""),0,IF(AND('Apostas - Grupos'!AB7='Jogos - Grupos'!F16,'Apostas - Grupos'!AC7='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB7='Apostas - Grupos'!AC7),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB7&gt;'Apostas - Grupos'!AC7),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB7&lt;'Apostas - Grupos'!AC7)),IF(('Apostas - Grupos'!AB7-'Apostas - Grupos'!AC7)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
@@ -14227,9 +14231,9 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X8="",'Apostas - Grupos'!Y8=""),0,IF(AND('Apostas - Grupos'!X8='Jogos - Grupos'!F14,'Apostas - Grupos'!Y8='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X8='Apostas - Grupos'!Y8),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X8&gt;'Apostas - Grupos'!Y8),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X8&lt;'Apostas - Grupos'!Y8)),IF(('Apostas - Grupos'!X8-'Apostas - Grupos'!Y8)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N8" s="108" t="str">
+      <c r="N8" s="108">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z8="",'Apostas - Grupos'!AA8=""),0,IF(AND('Apostas - Grupos'!Z8='Jogos - Grupos'!F15,'Apostas - Grupos'!AA8='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z8='Apostas - Grupos'!AA8),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z8&gt;'Apostas - Grupos'!AA8),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z8&lt;'Apostas - Grupos'!AA8)),IF(('Apostas - Grupos'!Z8-'Apostas - Grupos'!AA8)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="O8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB8="",'Apostas - Grupos'!AC8=""),0,IF(AND('Apostas - Grupos'!AB8='Jogos - Grupos'!F16,'Apostas - Grupos'!AC8='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB8='Apostas - Grupos'!AC8),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB8&gt;'Apostas - Grupos'!AC8),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB8&lt;'Apostas - Grupos'!AC8)),IF(('Apostas - Grupos'!AB8-'Apostas - Grupos'!AC8)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
@@ -14921,15 +14925,15 @@
       </c>
       <c r="D11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*(('Jogos - Grupos'!$D$3:$D$74=$B11)+('Jogos - Grupos'!$E$3:$E$74=$B11))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="114">
         <f t="shared" si="0"/>
@@ -14937,11 +14941,11 @@
       </c>
       <c r="H11" s="19">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="114">
         <f t="shared" si="2"/>
-        <v>200000495</v>
+        <v>1200001495</v>
       </c>
       <c r="J11" s="19">
         <f>RANK(I11,$I$11:$I$14,0)</f>
@@ -14964,15 +14968,15 @@
       </c>
       <c r="D12" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*(('Jogos - Grupos'!$D$3:$D$74=$B12)+('Jogos - Grupos'!$E$3:$E$74=$B12))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$D$3:$D$74=$B12)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$E$3:$E$74=$B12)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$D$3:$D$74=$B12)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$E$3:$E$74=$B12)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="114">
         <f t="shared" si="0"/>
@@ -14980,11 +14984,11 @@
       </c>
       <c r="H12" s="19">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="114">
         <f t="shared" si="2"/>
-        <v>200000486</v>
+        <v>1200001486</v>
       </c>
       <c r="J12" s="19">
         <f>RANK(I12,$I$11:$I$14,0)</f>

--- a/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\projetos\bolão_copa\gabarito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A06A87A-2EC0-4702-87B2-05DEFBAD04F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042B0E6B-764A-4FBC-A78A-D26B91125285}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="3000" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4976,67 +4976,73 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5045,22 +5051,13 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5076,6 +5073,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5836,7 +5836,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5972,67 +5972,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="273" t="s">
+      <c r="AH3" s="270" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="273" t="s">
+      <c r="AJ3" s="270" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="273" t="s">
+      <c r="AL3" s="270" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="273" t="s">
+      <c r="AN3" s="270" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="273" t="s">
+      <c r="AP3" s="270" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="273" t="s">
+      <c r="AR3" s="270" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="273" t="s">
+      <c r="AT3" s="270" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="273" t="s">
+      <c r="AV3" s="270" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="275" t="s">
+      <c r="AX3" s="274" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="275" t="s">
+      <c r="AZ3" s="274" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="275" t="s">
+      <c r="BB3" s="274" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="275" t="s">
+      <c r="BD3" s="274" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="281" t="s">
+      <c r="BF3" s="277" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="281" t="s">
+      <c r="BH3" s="277" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="279" t="s">
+      <c r="BJ3" s="273" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="280" t="s">
+      <c r="BL3" s="275" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -6041,131 +6041,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="270">
+      <c r="B4" s="272">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="270">
+      <c r="D4" s="272">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="270">
+      <c r="F4" s="272">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="270">
+      <c r="H4" s="272">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="270">
+      <c r="J4" s="272">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="270">
+      <c r="L4" s="272">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="270">
+      <c r="N4" s="272">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="270">
+      <c r="P4" s="272">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="270">
+      <c r="R4" s="272">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="270">
+      <c r="T4" s="272">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="270">
+      <c r="V4" s="272">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="270">
+      <c r="X4" s="272">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="270">
+      <c r="Z4" s="272">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="270">
+      <c r="AB4" s="272">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="270">
+      <c r="AD4" s="272">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="270">
+      <c r="AF4" s="272">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="274">
+      <c r="AH4" s="276">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="274">
+      <c r="AJ4" s="276">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="274">
+      <c r="AL4" s="276">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="274">
+      <c r="AN4" s="276">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="274">
+      <c r="AP4" s="276">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="274">
+      <c r="AR4" s="276">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="274">
+      <c r="AT4" s="276">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="274">
+      <c r="AV4" s="276">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="272">
+      <c r="AX4" s="278">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="272">
+      <c r="AZ4" s="278">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="272">
+      <c r="BB4" s="278">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="272">
+      <c r="BD4" s="278">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="277">
+      <c r="BF4" s="279">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="277">
+      <c r="BH4" s="279">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="276">
+      <c r="BJ4" s="281">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="278">
+      <c r="BL4" s="280">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7620,6 +7620,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="BJ4:BK4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
     <mergeCell ref="A2:BM2"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
@@ -7636,56 +7686,6 @@
     <mergeCell ref="BF3:BG3"/>
     <mergeCell ref="BH3:BI3"/>
     <mergeCell ref="V4:W4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="BJ4:BK4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7743,7 +7743,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8909,7 +8909,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8923,49 +8923,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1">
-      <c r="A4" s="284" t="s">
+      <c r="A4" s="289" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="284" t="s">
+      <c r="C4" s="289" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="284" t="s">
+      <c r="E4" s="289" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="284" t="s">
+      <c r="G4" s="289" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="284" t="s">
+      <c r="I4" s="289" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1">
-      <c r="A5" s="286" t="str">
+      <c r="A5" s="285" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="285">
+      <c r="C5" s="284">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="288">
+      <c r="E5" s="287">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="287">
+      <c r="G5" s="286">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="289" t="s">
+      <c r="I5" s="288" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9116,11 +9116,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9128,6 +9123,11 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9522,11 +9522,15 @@
       <c r="E16" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
+      <c r="F16" s="10">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10">
+        <v>1</v>
+      </c>
       <c r="H16" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -9664,11 +9668,15 @@
       <c r="E22" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+      <c r="F22" s="10">
+        <v>2</v>
+      </c>
+      <c r="G22" s="10">
+        <v>0</v>
+      </c>
       <c r="H22" s="26" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -11037,7 +11045,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11189,219 +11197,219 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="256" t="s">
+      <c r="B3" s="263" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="256" t="s">
+      <c r="D3" s="263" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="256" t="s">
+      <c r="F3" s="263" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="256" t="s">
+      <c r="H3" s="263" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="256" t="s">
+      <c r="J3" s="263" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="256" t="s">
+      <c r="L3" s="263" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="260" t="s">
+      <c r="N3" s="264" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="260" t="s">
+      <c r="P3" s="264" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="260" t="s">
+      <c r="R3" s="264" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="260" t="s">
+      <c r="T3" s="264" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="260" t="s">
+      <c r="V3" s="264" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="260" t="s">
+      <c r="X3" s="264" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="261" t="s">
+      <c r="Z3" s="259" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="261" t="s">
+      <c r="AB3" s="259" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="261" t="s">
+      <c r="AD3" s="259" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="261" t="s">
+      <c r="AF3" s="259" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="261" t="s">
+      <c r="AH3" s="259" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="261" t="s">
+      <c r="AJ3" s="259" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="257" t="s">
+      <c r="AL3" s="260" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="257" t="s">
+      <c r="AN3" s="260" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="257" t="s">
+      <c r="AP3" s="260" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="257" t="s">
+      <c r="AR3" s="260" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="257" t="s">
+      <c r="AT3" s="260" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="257" t="s">
+      <c r="AV3" s="260" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="258" t="s">
+      <c r="AX3" s="265" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="258" t="s">
+      <c r="AZ3" s="265" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="258" t="s">
+      <c r="BB3" s="265" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="258" t="s">
+      <c r="BD3" s="265" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="258" t="s">
+      <c r="BF3" s="265" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="258" t="s">
+      <c r="BH3" s="265" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="262" t="s">
+      <c r="BJ3" s="266" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="262" t="s">
+      <c r="BL3" s="266" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="262" t="s">
+      <c r="BN3" s="266" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="262" t="s">
+      <c r="BP3" s="266" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="262" t="s">
+      <c r="BR3" s="266" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="262" t="s">
+      <c r="BT3" s="266" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
-      <c r="BV3" s="263" t="s">
+      <c r="BV3" s="256" t="s">
         <v>224</v>
       </c>
       <c r="BW3" s="253"/>
-      <c r="BX3" s="263" t="s">
+      <c r="BX3" s="256" t="s">
         <v>225</v>
       </c>
       <c r="BY3" s="253"/>
-      <c r="BZ3" s="263" t="s">
+      <c r="BZ3" s="256" t="s">
         <v>226</v>
       </c>
       <c r="CA3" s="253"/>
-      <c r="CB3" s="263" t="s">
+      <c r="CB3" s="256" t="s">
         <v>227</v>
       </c>
       <c r="CC3" s="253"/>
-      <c r="CD3" s="263" t="s">
+      <c r="CD3" s="256" t="s">
         <v>228</v>
       </c>
       <c r="CE3" s="253"/>
-      <c r="CF3" s="263" t="s">
+      <c r="CF3" s="256" t="s">
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="259" t="s">
+      <c r="CH3" s="257" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="259" t="s">
+      <c r="CJ3" s="257" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="259" t="s">
+      <c r="CL3" s="257" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="259" t="s">
+      <c r="CN3" s="257" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="259" t="s">
+      <c r="CP3" s="257" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="259" t="s">
+      <c r="CR3" s="257" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
-      <c r="CT3" s="265" t="s">
+      <c r="CT3" s="258" t="s">
         <v>236</v>
       </c>
       <c r="CU3" s="253"/>
-      <c r="CV3" s="265" t="s">
+      <c r="CV3" s="258" t="s">
         <v>237</v>
       </c>
       <c r="CW3" s="253"/>
-      <c r="CX3" s="265" t="s">
+      <c r="CX3" s="258" t="s">
         <v>238</v>
       </c>
       <c r="CY3" s="253"/>
-      <c r="CZ3" s="265" t="s">
+      <c r="CZ3" s="258" t="s">
         <v>239</v>
       </c>
       <c r="DA3" s="253"/>
-      <c r="DB3" s="265" t="s">
+      <c r="DB3" s="258" t="s">
         <v>240</v>
       </c>
       <c r="DC3" s="253"/>
-      <c r="DD3" s="265" t="s">
+      <c r="DD3" s="258" t="s">
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
@@ -11429,51 +11437,51 @@
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="266" t="s">
+      <c r="DR3" s="268" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="266" t="s">
+      <c r="DT3" s="268" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="266" t="s">
+      <c r="DV3" s="268" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="266" t="s">
+      <c r="DX3" s="268" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="266" t="s">
+      <c r="DZ3" s="268" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="266" t="s">
+      <c r="EB3" s="268" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="264" t="s">
+      <c r="ED3" s="262" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="264" t="s">
+      <c r="EF3" s="262" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="264" t="s">
+      <c r="EH3" s="262" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="264" t="s">
+      <c r="EJ3" s="262" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="264" t="s">
+      <c r="EL3" s="262" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="264" t="s">
+      <c r="EN3" s="262" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12513,16 +12521,54 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="CJ3:CK3"/>
+    <mergeCell ref="CL3:CM3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="BT3:BU3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="CF3:CG3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="DN3:DO3"/>
+    <mergeCell ref="A1:EO1"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="CR3:CS3"/>
     <mergeCell ref="A2:EO2"/>
     <mergeCell ref="EJ3:EK3"/>
     <mergeCell ref="D3:E3"/>
@@ -12539,54 +12585,16 @@
     <mergeCell ref="DJ3:DK3"/>
     <mergeCell ref="EL3:EM3"/>
     <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="A1:EO1"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="CJ3:CK3"/>
-    <mergeCell ref="CL3:CM3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="BT3:BU3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="CF3:CG3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="CT3:CU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12612,7 +12620,7 @@
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12765,7 +12773,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>
@@ -13344,9 +13352,9 @@
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z5="",'Apostas - Grupos'!AA5=""),0,IF(AND('Apostas - Grupos'!Z5='Jogos - Grupos'!F15,'Apostas - Grupos'!AA5='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z5='Apostas - Grupos'!AA5),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z5&gt;'Apostas - Grupos'!AA5),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z5&lt;'Apostas - Grupos'!AA5)),IF(('Apostas - Grupos'!Z5-'Apostas - Grupos'!AA5)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="O5" s="106" t="str">
+      <c r="O5" s="106">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB5="",'Apostas - Grupos'!AC5=""),0,IF(AND('Apostas - Grupos'!AB5='Jogos - Grupos'!F16,'Apostas - Grupos'!AC5='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB5='Apostas - Grupos'!AC5),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB5&gt;'Apostas - Grupos'!AC5),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB5&lt;'Apostas - Grupos'!AC5)),IF(('Apostas - Grupos'!AB5-'Apostas - Grupos'!AC5)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="P5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD5="",'Apostas - Grupos'!AE5=""),0,IF(AND('Apostas - Grupos'!AD5='Jogos - Grupos'!F17,'Apostas - Grupos'!AE5='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD5='Apostas - Grupos'!AE5),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD5&gt;'Apostas - Grupos'!AE5),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD5&lt;'Apostas - Grupos'!AE5)),IF(('Apostas - Grupos'!AD5-'Apostas - Grupos'!AE5)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -13368,9 +13376,9 @@
         <f>IF(OR('Jogos - Grupos'!F21="",'Jogos - Grupos'!G21=""),"-",IF(OR('Apostas - Grupos'!AL5="",'Apostas - Grupos'!AM5=""),0,IF(AND('Apostas - Grupos'!AL5='Jogos - Grupos'!F21,'Apostas - Grupos'!AM5='Jogos - Grupos'!G21),5,IF(OR(AND('Jogos - Grupos'!F21='Jogos - Grupos'!G21,'Apostas - Grupos'!AL5='Apostas - Grupos'!AM5),AND('Jogos - Grupos'!F21&gt;'Jogos - Grupos'!G21,'Apostas - Grupos'!AL5&gt;'Apostas - Grupos'!AM5),AND('Jogos - Grupos'!F21&lt;'Jogos - Grupos'!G21,'Apostas - Grupos'!AL5&lt;'Apostas - Grupos'!AM5)),IF(('Apostas - Grupos'!AL5-'Apostas - Grupos'!AM5)=('Jogos - Grupos'!F21-'Jogos - Grupos'!G21),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="U5" s="106" t="str">
+      <c r="U5" s="106">
         <f>IF(OR('Jogos - Grupos'!F22="",'Jogos - Grupos'!G22=""),"-",IF(OR('Apostas - Grupos'!AN5="",'Apostas - Grupos'!AO5=""),0,IF(AND('Apostas - Grupos'!AN5='Jogos - Grupos'!F22,'Apostas - Grupos'!AO5='Jogos - Grupos'!G22),5,IF(OR(AND('Jogos - Grupos'!F22='Jogos - Grupos'!G22,'Apostas - Grupos'!AN5='Apostas - Grupos'!AO5),AND('Jogos - Grupos'!F22&gt;'Jogos - Grupos'!G22,'Apostas - Grupos'!AN5&gt;'Apostas - Grupos'!AO5),AND('Jogos - Grupos'!F22&lt;'Jogos - Grupos'!G22,'Apostas - Grupos'!AN5&lt;'Apostas - Grupos'!AO5)),IF(('Apostas - Grupos'!AN5-'Apostas - Grupos'!AO5)=('Jogos - Grupos'!F22-'Jogos - Grupos'!G22),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="V5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F23="",'Jogos - Grupos'!G23=""),"-",IF(OR('Apostas - Grupos'!AP5="",'Apostas - Grupos'!AQ5=""),0,IF(AND('Apostas - Grupos'!AP5='Jogos - Grupos'!F23,'Apostas - Grupos'!AQ5='Jogos - Grupos'!G23),5,IF(OR(AND('Jogos - Grupos'!F23='Jogos - Grupos'!G23,'Apostas - Grupos'!AP5='Apostas - Grupos'!AQ5),AND('Jogos - Grupos'!F23&gt;'Jogos - Grupos'!G23,'Apostas - Grupos'!AP5&gt;'Apostas - Grupos'!AQ5),AND('Jogos - Grupos'!F23&lt;'Jogos - Grupos'!G23,'Apostas - Grupos'!AP5&lt;'Apostas - Grupos'!AQ5)),IF(('Apostas - Grupos'!AP5-'Apostas - Grupos'!AQ5)=('Jogos - Grupos'!F23-'Jogos - Grupos'!G23),3,2),0))))</f>
@@ -13641,9 +13649,9 @@
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z6="",'Apostas - Grupos'!AA6=""),0,IF(AND('Apostas - Grupos'!Z6='Jogos - Grupos'!F15,'Apostas - Grupos'!AA6='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z6='Apostas - Grupos'!AA6),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z6&gt;'Apostas - Grupos'!AA6),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z6&lt;'Apostas - Grupos'!AA6)),IF(('Apostas - Grupos'!Z6-'Apostas - Grupos'!AA6)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="O6" s="108" t="str">
+      <c r="O6" s="108">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB6="",'Apostas - Grupos'!AC6=""),0,IF(AND('Apostas - Grupos'!AB6='Jogos - Grupos'!F16,'Apostas - Grupos'!AC6='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB6='Apostas - Grupos'!AC6),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB6&gt;'Apostas - Grupos'!AC6),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB6&lt;'Apostas - Grupos'!AC6)),IF(('Apostas - Grupos'!AB6-'Apostas - Grupos'!AC6)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="P6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD6="",'Apostas - Grupos'!AE6=""),0,IF(AND('Apostas - Grupos'!AD6='Jogos - Grupos'!F17,'Apostas - Grupos'!AE6='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD6='Apostas - Grupos'!AE6),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD6&gt;'Apostas - Grupos'!AE6),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD6&lt;'Apostas - Grupos'!AE6)),IF(('Apostas - Grupos'!AD6-'Apostas - Grupos'!AE6)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -13665,9 +13673,9 @@
         <f>IF(OR('Jogos - Grupos'!F21="",'Jogos - Grupos'!G21=""),"-",IF(OR('Apostas - Grupos'!AL6="",'Apostas - Grupos'!AM6=""),0,IF(AND('Apostas - Grupos'!AL6='Jogos - Grupos'!F21,'Apostas - Grupos'!AM6='Jogos - Grupos'!G21),5,IF(OR(AND('Jogos - Grupos'!F21='Jogos - Grupos'!G21,'Apostas - Grupos'!AL6='Apostas - Grupos'!AM6),AND('Jogos - Grupos'!F21&gt;'Jogos - Grupos'!G21,'Apostas - Grupos'!AL6&gt;'Apostas - Grupos'!AM6),AND('Jogos - Grupos'!F21&lt;'Jogos - Grupos'!G21,'Apostas - Grupos'!AL6&lt;'Apostas - Grupos'!AM6)),IF(('Apostas - Grupos'!AL6-'Apostas - Grupos'!AM6)=('Jogos - Grupos'!F21-'Jogos - Grupos'!G21),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="U6" s="108" t="str">
+      <c r="U6" s="108">
         <f>IF(OR('Jogos - Grupos'!F22="",'Jogos - Grupos'!G22=""),"-",IF(OR('Apostas - Grupos'!AN6="",'Apostas - Grupos'!AO6=""),0,IF(AND('Apostas - Grupos'!AN6='Jogos - Grupos'!F22,'Apostas - Grupos'!AO6='Jogos - Grupos'!G22),5,IF(OR(AND('Jogos - Grupos'!F22='Jogos - Grupos'!G22,'Apostas - Grupos'!AN6='Apostas - Grupos'!AO6),AND('Jogos - Grupos'!F22&gt;'Jogos - Grupos'!G22,'Apostas - Grupos'!AN6&gt;'Apostas - Grupos'!AO6),AND('Jogos - Grupos'!F22&lt;'Jogos - Grupos'!G22,'Apostas - Grupos'!AN6&lt;'Apostas - Grupos'!AO6)),IF(('Apostas - Grupos'!AN6-'Apostas - Grupos'!AO6)=('Jogos - Grupos'!F22-'Jogos - Grupos'!G22),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="V6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F23="",'Jogos - Grupos'!G23=""),"-",IF(OR('Apostas - Grupos'!AP6="",'Apostas - Grupos'!AQ6=""),0,IF(AND('Apostas - Grupos'!AP6='Jogos - Grupos'!F23,'Apostas - Grupos'!AQ6='Jogos - Grupos'!G23),5,IF(OR(AND('Jogos - Grupos'!F23='Jogos - Grupos'!G23,'Apostas - Grupos'!AP6='Apostas - Grupos'!AQ6),AND('Jogos - Grupos'!F23&gt;'Jogos - Grupos'!G23,'Apostas - Grupos'!AP6&gt;'Apostas - Grupos'!AQ6),AND('Jogos - Grupos'!F23&lt;'Jogos - Grupos'!G23,'Apostas - Grupos'!AP6&lt;'Apostas - Grupos'!AQ6)),IF(('Apostas - Grupos'!AP6-'Apostas - Grupos'!AQ6)=('Jogos - Grupos'!F23-'Jogos - Grupos'!G23),3,2),0))))</f>
@@ -13938,9 +13946,9 @@
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z7="",'Apostas - Grupos'!AA7=""),0,IF(AND('Apostas - Grupos'!Z7='Jogos - Grupos'!F15,'Apostas - Grupos'!AA7='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z7='Apostas - Grupos'!AA7),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z7&gt;'Apostas - Grupos'!AA7),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z7&lt;'Apostas - Grupos'!AA7)),IF(('Apostas - Grupos'!Z7-'Apostas - Grupos'!AA7)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="O7" s="106" t="str">
+      <c r="O7" s="106">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB7="",'Apostas - Grupos'!AC7=""),0,IF(AND('Apostas - Grupos'!AB7='Jogos - Grupos'!F16,'Apostas - Grupos'!AC7='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB7='Apostas - Grupos'!AC7),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB7&gt;'Apostas - Grupos'!AC7),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB7&lt;'Apostas - Grupos'!AC7)),IF(('Apostas - Grupos'!AB7-'Apostas - Grupos'!AC7)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="P7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD7="",'Apostas - Grupos'!AE7=""),0,IF(AND('Apostas - Grupos'!AD7='Jogos - Grupos'!F17,'Apostas - Grupos'!AE7='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD7='Apostas - Grupos'!AE7),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD7&gt;'Apostas - Grupos'!AE7),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD7&lt;'Apostas - Grupos'!AE7)),IF(('Apostas - Grupos'!AD7-'Apostas - Grupos'!AE7)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -13962,9 +13970,9 @@
         <f>IF(OR('Jogos - Grupos'!F21="",'Jogos - Grupos'!G21=""),"-",IF(OR('Apostas - Grupos'!AL7="",'Apostas - Grupos'!AM7=""),0,IF(AND('Apostas - Grupos'!AL7='Jogos - Grupos'!F21,'Apostas - Grupos'!AM7='Jogos - Grupos'!G21),5,IF(OR(AND('Jogos - Grupos'!F21='Jogos - Grupos'!G21,'Apostas - Grupos'!AL7='Apostas - Grupos'!AM7),AND('Jogos - Grupos'!F21&gt;'Jogos - Grupos'!G21,'Apostas - Grupos'!AL7&gt;'Apostas - Grupos'!AM7),AND('Jogos - Grupos'!F21&lt;'Jogos - Grupos'!G21,'Apostas - Grupos'!AL7&lt;'Apostas - Grupos'!AM7)),IF(('Apostas - Grupos'!AL7-'Apostas - Grupos'!AM7)=('Jogos - Grupos'!F21-'Jogos - Grupos'!G21),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="U7" s="106" t="str">
+      <c r="U7" s="106">
         <f>IF(OR('Jogos - Grupos'!F22="",'Jogos - Grupos'!G22=""),"-",IF(OR('Apostas - Grupos'!AN7="",'Apostas - Grupos'!AO7=""),0,IF(AND('Apostas - Grupos'!AN7='Jogos - Grupos'!F22,'Apostas - Grupos'!AO7='Jogos - Grupos'!G22),5,IF(OR(AND('Jogos - Grupos'!F22='Jogos - Grupos'!G22,'Apostas - Grupos'!AN7='Apostas - Grupos'!AO7),AND('Jogos - Grupos'!F22&gt;'Jogos - Grupos'!G22,'Apostas - Grupos'!AN7&gt;'Apostas - Grupos'!AO7),AND('Jogos - Grupos'!F22&lt;'Jogos - Grupos'!G22,'Apostas - Grupos'!AN7&lt;'Apostas - Grupos'!AO7)),IF(('Apostas - Grupos'!AN7-'Apostas - Grupos'!AO7)=('Jogos - Grupos'!F22-'Jogos - Grupos'!G22),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="V7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F23="",'Jogos - Grupos'!G23=""),"-",IF(OR('Apostas - Grupos'!AP7="",'Apostas - Grupos'!AQ7=""),0,IF(AND('Apostas - Grupos'!AP7='Jogos - Grupos'!F23,'Apostas - Grupos'!AQ7='Jogos - Grupos'!G23),5,IF(OR(AND('Jogos - Grupos'!F23='Jogos - Grupos'!G23,'Apostas - Grupos'!AP7='Apostas - Grupos'!AQ7),AND('Jogos - Grupos'!F23&gt;'Jogos - Grupos'!G23,'Apostas - Grupos'!AP7&gt;'Apostas - Grupos'!AQ7),AND('Jogos - Grupos'!F23&lt;'Jogos - Grupos'!G23,'Apostas - Grupos'!AP7&lt;'Apostas - Grupos'!AQ7)),IF(('Apostas - Grupos'!AP7-'Apostas - Grupos'!AQ7)=('Jogos - Grupos'!F23-'Jogos - Grupos'!G23),3,2),0))))</f>
@@ -14235,9 +14243,9 @@
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z8="",'Apostas - Grupos'!AA8=""),0,IF(AND('Apostas - Grupos'!Z8='Jogos - Grupos'!F15,'Apostas - Grupos'!AA8='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z8='Apostas - Grupos'!AA8),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z8&gt;'Apostas - Grupos'!AA8),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z8&lt;'Apostas - Grupos'!AA8)),IF(('Apostas - Grupos'!Z8-'Apostas - Grupos'!AA8)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="108" t="str">
+      <c r="O8" s="108">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB8="",'Apostas - Grupos'!AC8=""),0,IF(AND('Apostas - Grupos'!AB8='Jogos - Grupos'!F16,'Apostas - Grupos'!AC8='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB8='Apostas - Grupos'!AC8),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB8&gt;'Apostas - Grupos'!AC8),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB8&lt;'Apostas - Grupos'!AC8)),IF(('Apostas - Grupos'!AB8-'Apostas - Grupos'!AC8)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="P8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD8="",'Apostas - Grupos'!AE8=""),0,IF(AND('Apostas - Grupos'!AD8='Jogos - Grupos'!F17,'Apostas - Grupos'!AE8='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD8='Apostas - Grupos'!AE8),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD8&gt;'Apostas - Grupos'!AE8),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD8&lt;'Apostas - Grupos'!AE8)),IF(('Apostas - Grupos'!AD8-'Apostas - Grupos'!AE8)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -14259,9 +14267,9 @@
         <f>IF(OR('Jogos - Grupos'!F21="",'Jogos - Grupos'!G21=""),"-",IF(OR('Apostas - Grupos'!AL8="",'Apostas - Grupos'!AM8=""),0,IF(AND('Apostas - Grupos'!AL8='Jogos - Grupos'!F21,'Apostas - Grupos'!AM8='Jogos - Grupos'!G21),5,IF(OR(AND('Jogos - Grupos'!F21='Jogos - Grupos'!G21,'Apostas - Grupos'!AL8='Apostas - Grupos'!AM8),AND('Jogos - Grupos'!F21&gt;'Jogos - Grupos'!G21,'Apostas - Grupos'!AL8&gt;'Apostas - Grupos'!AM8),AND('Jogos - Grupos'!F21&lt;'Jogos - Grupos'!G21,'Apostas - Grupos'!AL8&lt;'Apostas - Grupos'!AM8)),IF(('Apostas - Grupos'!AL8-'Apostas - Grupos'!AM8)=('Jogos - Grupos'!F21-'Jogos - Grupos'!G21),3,2),0))))</f>
         <v>0</v>
       </c>
-      <c r="U8" s="108" t="str">
+      <c r="U8" s="108">
         <f>IF(OR('Jogos - Grupos'!F22="",'Jogos - Grupos'!G22=""),"-",IF(OR('Apostas - Grupos'!AN8="",'Apostas - Grupos'!AO8=""),0,IF(AND('Apostas - Grupos'!AN8='Jogos - Grupos'!F22,'Apostas - Grupos'!AO8='Jogos - Grupos'!G22),5,IF(OR(AND('Jogos - Grupos'!F22='Jogos - Grupos'!G22,'Apostas - Grupos'!AN8='Apostas - Grupos'!AO8),AND('Jogos - Grupos'!F22&gt;'Jogos - Grupos'!G22,'Apostas - Grupos'!AN8&gt;'Apostas - Grupos'!AO8),AND('Jogos - Grupos'!F22&lt;'Jogos - Grupos'!G22,'Apostas - Grupos'!AN8&lt;'Apostas - Grupos'!AO8)),IF(('Apostas - Grupos'!AN8-'Apostas - Grupos'!AO8)=('Jogos - Grupos'!F22-'Jogos - Grupos'!G22),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="V8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F23="",'Jogos - Grupos'!G23=""),"-",IF(OR('Apostas - Grupos'!AP8="",'Apostas - Grupos'!AQ8=""),0,IF(AND('Apostas - Grupos'!AP8='Jogos - Grupos'!F23,'Apostas - Grupos'!AQ8='Jogos - Grupos'!G23),5,IF(OR(AND('Jogos - Grupos'!F23='Jogos - Grupos'!G23,'Apostas - Grupos'!AP8='Apostas - Grupos'!AQ8),AND('Jogos - Grupos'!F23&gt;'Jogos - Grupos'!G23,'Apostas - Grupos'!AP8&gt;'Apostas - Grupos'!AQ8),AND('Jogos - Grupos'!F23&lt;'Jogos - Grupos'!G23,'Apostas - Grupos'!AP8&lt;'Apostas - Grupos'!AQ8)),IF(('Apostas - Grupos'!AP8-'Apostas - Grupos'!AQ8)=('Jogos - Grupos'!F23-'Jogos - Grupos'!G23),3,2),0))))</f>
@@ -14949,7 +14957,7 @@
       </c>
       <c r="J11" s="19">
         <f>RANK(I11,$I$11:$I$14,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="114">
         <v>5</v>
@@ -14992,7 +15000,7 @@
       </c>
       <c r="J12" s="19">
         <f>RANK(I12,$I$11:$I$14,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="114">
         <v>14</v>
@@ -15019,11 +15027,11 @@
       </c>
       <c r="F13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$D$3:$D$74=$B13)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$E$3:$E$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="114">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H13" s="19">
         <f t="shared" si="1"/>
@@ -15031,7 +15039,7 @@
       </c>
       <c r="I13" s="114">
         <f t="shared" si="2"/>
-        <v>200000414</v>
+        <v>199000414</v>
       </c>
       <c r="J13" s="19">
         <f>RANK(I13,$I$11:$I$14,0)</f>
@@ -15050,7 +15058,7 @@
       </c>
       <c r="C14" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$D$3:$D$74=$B14)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$E$3:$E$74=$B14)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*(('Jogos - Grupos'!$D$3:$D$74=$B14)+('Jogos - Grupos'!$E$3:$E$74=$B14))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -15058,7 +15066,7 @@
       </c>
       <c r="E14" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$D$3:$D$74=$B14)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$E$3:$E$74=$B14)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$D$3:$D$74=$B14)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$E$3:$E$74=$B14)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
@@ -15066,19 +15074,19 @@
       </c>
       <c r="G14" s="114">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="19">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" s="114">
         <f t="shared" si="2"/>
-        <v>200000473</v>
+        <v>3201001473</v>
       </c>
       <c r="J14" s="19">
         <f>RANK(I14,$I$11:$I$14,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14" s="114">
         <v>27</v>
@@ -15179,7 +15187,7 @@
       </c>
       <c r="C17" s="116">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A17)*('Jogos - Grupos'!$D$3:$D$74=$B17)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A17)*('Jogos - Grupos'!$E$3:$E$74=$B17)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="116">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A17)*(('Jogos - Grupos'!$D$3:$D$74=$B17)+('Jogos - Grupos'!$E$3:$E$74=$B17))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -15187,7 +15195,7 @@
       </c>
       <c r="E17" s="116">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A17)*('Jogos - Grupos'!$D$3:$D$74=$B17)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A17)*('Jogos - Grupos'!$E$3:$E$74=$B17)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="116">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A17)*('Jogos - Grupos'!$D$3:$D$74=$B17)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A17)*('Jogos - Grupos'!$E$3:$E$74=$B17)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
@@ -15195,15 +15203,15 @@
       </c>
       <c r="G17" s="116">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" s="116">
         <f t="shared" si="2"/>
-        <v>200000477</v>
+        <v>3202002477</v>
       </c>
       <c r="J17" s="24">
         <f>RANK(I17,$I$15:$I$18,0)</f>
@@ -15234,11 +15242,11 @@
       </c>
       <c r="F18" s="116">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A18)*('Jogos - Grupos'!$D$3:$D$74=$B18)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A18)*('Jogos - Grupos'!$E$3:$E$74=$B18)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="116">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H18" s="24">
         <f t="shared" si="1"/>
@@ -15246,7 +15254,7 @@
       </c>
       <c r="I18" s="116">
         <f t="shared" si="2"/>
-        <v>200000464</v>
+        <v>198000464</v>
       </c>
       <c r="J18" s="24">
         <f>RANK(I18,$I$15:$I$18,0)</f>
@@ -16697,15 +16705,15 @@
       </c>
       <c r="B55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(1,$J$11:$J$14,0)),"?")</f>
-        <v>Brasil</v>
+        <v>Escocia</v>
       </c>
       <c r="C55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(2,$J$11:$J$14,0)),"?")</f>
-        <v>Marrocos</v>
+        <v>Brasil</v>
       </c>
       <c r="D55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(3,$J$11:$J$14,0)),"?")</f>
-        <v>Escocia</v>
+        <v>Marrocos</v>
       </c>
       <c r="E55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(4,$J$11:$J$14,0)),"?")</f>
@@ -16929,7 +16937,7 @@
       </c>
       <c r="D68" s="150">
         <f t="shared" ref="D68:D79" si="3">RANK(C68,$C$68:$C$79,0)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -16946,7 +16954,7 @@
       </c>
       <c r="D69" s="150">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -16955,15 +16963,15 @@
       </c>
       <c r="B70" s="149" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(3,$J$11:$J$14,0)),"?")</f>
-        <v>Escocia</v>
+        <v>Marrocos</v>
       </c>
       <c r="C70" s="149">
         <f>IFERROR(INDEX($I$11:$I$14,MATCH(3,$J$11:$J$14,0)),0)</f>
-        <v>200000473</v>
+        <v>1200001486</v>
       </c>
       <c r="D70" s="150">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -16976,11 +16984,11 @@
       </c>
       <c r="C71" s="149">
         <f>IFERROR(INDEX($I$15:$I$18,MATCH(3,$J$15:$J$18,0)),0)</f>
-        <v>200000464</v>
+        <v>198000464</v>
       </c>
       <c r="D71" s="150">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -16997,7 +17005,7 @@
       </c>
       <c r="D72" s="150">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -17014,7 +17022,7 @@
       </c>
       <c r="D73" s="150">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -17048,7 +17056,7 @@
       </c>
       <c r="D75" s="150">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -17099,7 +17107,7 @@
       </c>
       <c r="D78" s="150">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -17116,7 +17124,7 @@
       </c>
       <c r="D79" s="150">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -17133,7 +17141,7 @@
       </c>
       <c r="B82" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(1,$D$68:$D$79,0)),"?")</f>
-        <v>Canada</v>
+        <v>Marrocos</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -17142,7 +17150,7 @@
       </c>
       <c r="B83" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(2,$D$68:$D$79,0)),"?")</f>
-        <v>Suecia</v>
+        <v>Canada</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -17151,7 +17159,7 @@
       </c>
       <c r="B84" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(3,$D$68:$D$79,0)),"?")</f>
-        <v>Escocia</v>
+        <v>Suecia</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -17178,7 +17186,7 @@
       </c>
       <c r="B87" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(6,$D$68:$D$79,0)),"?")</f>
-        <v>Turquia</v>
+        <v>Egito</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -17187,7 +17195,7 @@
       </c>
       <c r="B88" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(7,$D$68:$D$79,0)),"?")</f>
-        <v>?</v>
+        <v>Costa do Marfim</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -17196,7 +17204,7 @@
       </c>
       <c r="B89" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(8,$D$68:$D$79,0)),"?")</f>
-        <v>Costa do Marfim</v>
+        <v>Gana</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -17205,7 +17213,7 @@
       </c>
       <c r="B92" s="166" t="str">
         <f>IF(D68&lt;=8,"A","")&amp;IF(D69&lt;=8,"B","")&amp;IF(D70&lt;=8,"C","")&amp;IF(D71&lt;=8,"D","")&amp;IF(D72&lt;=8,"E","")&amp;IF(D73&lt;=8,"F","")&amp;IF(D74&lt;=8,"G","")&amp;IF(D75&lt;=8,"H","")&amp;IF(D76&lt;=8,"I","")&amp;IF(D77&lt;=8,"J","")&amp;IF(D78&lt;=8,"K","")&amp;IF(D79&lt;=8,"L","")</f>
-        <v>BCDEFGIJ</v>
+        <v>BCEFGIJL</v>
       </c>
     </row>
   </sheetData>
@@ -43748,7 +43756,7 @@
       </c>
       <c r="E5" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,5,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Turquia</v>
+        <v>Marrocos</v>
       </c>
       <c r="F5" s="249"/>
       <c r="G5" s="249"/>
@@ -43778,7 +43786,7 @@
       </c>
       <c r="E6" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C55,"Aguardando")</f>
-        <v>Marrocos</v>
+        <v>Brasil</v>
       </c>
       <c r="F6" s="249"/>
       <c r="G6" s="249"/>
@@ -43804,7 +43812,7 @@
       </c>
       <c r="D7" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!B55,"Aguardando")</f>
-        <v>Brasil</v>
+        <v>Escocia</v>
       </c>
       <c r="E7" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C58,"Aguardando")</f>
@@ -43898,7 +43906,7 @@
       </c>
       <c r="E10" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,2,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Escocia</v>
+        <v>Costa do Marfim</v>
       </c>
       <c r="F10" s="249"/>
       <c r="G10" s="249"/>
@@ -44138,7 +44146,7 @@
       </c>
       <c r="E18" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,8,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Costa do Marfim</v>
+        <v>Gana</v>
       </c>
       <c r="F18" s="249"/>
       <c r="G18" s="249"/>

--- a/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\projetos\bolão_copa\gabarito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042B0E6B-764A-4FBC-A78A-D26B91125285}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B78E8AA-36C5-4E10-89B9-64B2AC722D41}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="3000" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regras" sheetId="1" r:id="rId1"/>
@@ -4976,73 +4976,67 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5051,13 +5045,22 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5073,9 +5076,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5836,7 +5836,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5972,67 +5972,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="270" t="s">
+      <c r="AH3" s="273" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="270" t="s">
+      <c r="AJ3" s="273" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="270" t="s">
+      <c r="AL3" s="273" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="270" t="s">
+      <c r="AN3" s="273" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="270" t="s">
+      <c r="AP3" s="273" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="270" t="s">
+      <c r="AR3" s="273" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="270" t="s">
+      <c r="AT3" s="273" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="270" t="s">
+      <c r="AV3" s="273" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="274" t="s">
+      <c r="AX3" s="275" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="274" t="s">
+      <c r="AZ3" s="275" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="274" t="s">
+      <c r="BB3" s="275" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="274" t="s">
+      <c r="BD3" s="275" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="277" t="s">
+      <c r="BF3" s="281" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="277" t="s">
+      <c r="BH3" s="281" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="273" t="s">
+      <c r="BJ3" s="279" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="275" t="s">
+      <c r="BL3" s="280" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -6041,131 +6041,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="272">
+      <c r="B4" s="270">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="272">
+      <c r="D4" s="270">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="272">
+      <c r="F4" s="270">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="272">
+      <c r="H4" s="270">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="272">
+      <c r="J4" s="270">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="272">
+      <c r="L4" s="270">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="272">
+      <c r="N4" s="270">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="272">
+      <c r="P4" s="270">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="272">
+      <c r="R4" s="270">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="272">
+      <c r="T4" s="270">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="272">
+      <c r="V4" s="270">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="272">
+      <c r="X4" s="270">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="272">
+      <c r="Z4" s="270">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="272">
+      <c r="AB4" s="270">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="272">
+      <c r="AD4" s="270">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="272">
+      <c r="AF4" s="270">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="276">
+      <c r="AH4" s="274">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="276">
+      <c r="AJ4" s="274">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="276">
+      <c r="AL4" s="274">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="276">
+      <c r="AN4" s="274">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="276">
+      <c r="AP4" s="274">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="276">
+      <c r="AR4" s="274">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="276">
+      <c r="AT4" s="274">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="276">
+      <c r="AV4" s="274">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="278">
+      <c r="AX4" s="272">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="278">
+      <c r="AZ4" s="272">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="278">
+      <c r="BB4" s="272">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="278">
+      <c r="BD4" s="272">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="279">
+      <c r="BF4" s="277">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="279">
+      <c r="BH4" s="277">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="281">
+      <c r="BJ4" s="276">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="280">
+      <c r="BL4" s="278">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7620,19 +7620,43 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="A2:BM2"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
@@ -7649,43 +7673,19 @@
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="AV3:AW3"/>
     <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="A2:BM2"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7743,7 +7743,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8909,7 +8909,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8923,49 +8923,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1">
-      <c r="A4" s="289" t="s">
+      <c r="A4" s="284" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="289" t="s">
+      <c r="C4" s="284" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="289" t="s">
+      <c r="E4" s="284" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="289" t="s">
+      <c r="G4" s="284" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="289" t="s">
+      <c r="I4" s="284" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1">
-      <c r="A5" s="285" t="str">
+      <c r="A5" s="286" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="284">
+      <c r="C5" s="285">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="287">
+      <c r="E5" s="288">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="286">
+      <c r="G5" s="287">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="288" t="s">
+      <c r="I5" s="289" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9116,6 +9116,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9123,11 +9128,6 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9787,11 +9787,15 @@
       <c r="E27" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
+      <c r="F27" s="10">
+        <v>7</v>
+      </c>
+      <c r="G27" s="10">
+        <v>1</v>
+      </c>
       <c r="H27" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -11045,7 +11049,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11197,219 +11201,219 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="263" t="s">
+      <c r="B3" s="256" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="263" t="s">
+      <c r="D3" s="256" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="263" t="s">
+      <c r="F3" s="256" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="263" t="s">
+      <c r="H3" s="256" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="263" t="s">
+      <c r="J3" s="256" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="263" t="s">
+      <c r="L3" s="256" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="264" t="s">
+      <c r="N3" s="260" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="264" t="s">
+      <c r="P3" s="260" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="264" t="s">
+      <c r="R3" s="260" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="260" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="264" t="s">
+      <c r="V3" s="260" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="264" t="s">
+      <c r="X3" s="260" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="259" t="s">
+      <c r="Z3" s="261" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="259" t="s">
+      <c r="AB3" s="261" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="259" t="s">
+      <c r="AD3" s="261" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="259" t="s">
+      <c r="AF3" s="261" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="259" t="s">
+      <c r="AH3" s="261" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="259" t="s">
+      <c r="AJ3" s="261" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="260" t="s">
+      <c r="AL3" s="257" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="260" t="s">
+      <c r="AN3" s="257" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="260" t="s">
+      <c r="AP3" s="257" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="260" t="s">
+      <c r="AR3" s="257" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="260" t="s">
+      <c r="AT3" s="257" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="260" t="s">
+      <c r="AV3" s="257" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="265" t="s">
+      <c r="AX3" s="258" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="265" t="s">
+      <c r="AZ3" s="258" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="265" t="s">
+      <c r="BB3" s="258" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="265" t="s">
+      <c r="BD3" s="258" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="265" t="s">
+      <c r="BF3" s="258" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="265" t="s">
+      <c r="BH3" s="258" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="266" t="s">
+      <c r="BJ3" s="262" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="266" t="s">
+      <c r="BL3" s="262" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="266" t="s">
+      <c r="BN3" s="262" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="266" t="s">
+      <c r="BP3" s="262" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="266" t="s">
+      <c r="BR3" s="262" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="266" t="s">
+      <c r="BT3" s="262" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
-      <c r="BV3" s="256" t="s">
+      <c r="BV3" s="263" t="s">
         <v>224</v>
       </c>
       <c r="BW3" s="253"/>
-      <c r="BX3" s="256" t="s">
+      <c r="BX3" s="263" t="s">
         <v>225</v>
       </c>
       <c r="BY3" s="253"/>
-      <c r="BZ3" s="256" t="s">
+      <c r="BZ3" s="263" t="s">
         <v>226</v>
       </c>
       <c r="CA3" s="253"/>
-      <c r="CB3" s="256" t="s">
+      <c r="CB3" s="263" t="s">
         <v>227</v>
       </c>
       <c r="CC3" s="253"/>
-      <c r="CD3" s="256" t="s">
+      <c r="CD3" s="263" t="s">
         <v>228</v>
       </c>
       <c r="CE3" s="253"/>
-      <c r="CF3" s="256" t="s">
+      <c r="CF3" s="263" t="s">
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="257" t="s">
+      <c r="CH3" s="259" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="257" t="s">
+      <c r="CJ3" s="259" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="257" t="s">
+      <c r="CL3" s="259" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="257" t="s">
+      <c r="CN3" s="259" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="257" t="s">
+      <c r="CP3" s="259" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="257" t="s">
+      <c r="CR3" s="259" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
-      <c r="CT3" s="258" t="s">
+      <c r="CT3" s="265" t="s">
         <v>236</v>
       </c>
       <c r="CU3" s="253"/>
-      <c r="CV3" s="258" t="s">
+      <c r="CV3" s="265" t="s">
         <v>237</v>
       </c>
       <c r="CW3" s="253"/>
-      <c r="CX3" s="258" t="s">
+      <c r="CX3" s="265" t="s">
         <v>238</v>
       </c>
       <c r="CY3" s="253"/>
-      <c r="CZ3" s="258" t="s">
+      <c r="CZ3" s="265" t="s">
         <v>239</v>
       </c>
       <c r="DA3" s="253"/>
-      <c r="DB3" s="258" t="s">
+      <c r="DB3" s="265" t="s">
         <v>240</v>
       </c>
       <c r="DC3" s="253"/>
-      <c r="DD3" s="258" t="s">
+      <c r="DD3" s="265" t="s">
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
@@ -11437,51 +11441,51 @@
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="268" t="s">
+      <c r="DR3" s="266" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="268" t="s">
+      <c r="DT3" s="266" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="268" t="s">
+      <c r="DV3" s="266" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="268" t="s">
+      <c r="DX3" s="266" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="268" t="s">
+      <c r="DZ3" s="266" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="268" t="s">
+      <c r="EB3" s="266" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="262" t="s">
+      <c r="ED3" s="264" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="262" t="s">
+      <c r="EF3" s="264" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="262" t="s">
+      <c r="EH3" s="264" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="262" t="s">
+      <c r="EJ3" s="264" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="262" t="s">
+      <c r="EL3" s="264" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="262" t="s">
+      <c r="EN3" s="264" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12521,6 +12525,64 @@
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="A2:EO2"/>
+    <mergeCell ref="EJ3:EK3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="DL3:DM3"/>
+    <mergeCell ref="BV3:BW3"/>
+    <mergeCell ref="CB3:CC3"/>
+    <mergeCell ref="DJ3:DK3"/>
+    <mergeCell ref="EL3:EM3"/>
+    <mergeCell ref="CV3:CW3"/>
+    <mergeCell ref="A1:EO1"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="CR3:CS3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="DN3:DO3"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
@@ -12537,64 +12599,6 @@
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="A1:EO1"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="A2:EO2"/>
-    <mergeCell ref="EJ3:EK3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="DL3:DM3"/>
-    <mergeCell ref="BV3:BW3"/>
-    <mergeCell ref="CB3:CC3"/>
-    <mergeCell ref="DJ3:DK3"/>
-    <mergeCell ref="EL3:EM3"/>
-    <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="CT3:CU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12620,7 +12624,7 @@
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12773,7 +12777,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>
@@ -13396,9 +13400,9 @@
         <f>IF(OR('Jogos - Grupos'!F26="",'Jogos - Grupos'!G26=""),"-",IF(OR('Apostas - Grupos'!AV5="",'Apostas - Grupos'!AW5=""),0,IF(AND('Apostas - Grupos'!AV5='Jogos - Grupos'!F26,'Apostas - Grupos'!AW5='Jogos - Grupos'!G26),5,IF(OR(AND('Jogos - Grupos'!F26='Jogos - Grupos'!G26,'Apostas - Grupos'!AV5='Apostas - Grupos'!AW5),AND('Jogos - Grupos'!F26&gt;'Jogos - Grupos'!G26,'Apostas - Grupos'!AV5&gt;'Apostas - Grupos'!AW5),AND('Jogos - Grupos'!F26&lt;'Jogos - Grupos'!G26,'Apostas - Grupos'!AV5&lt;'Apostas - Grupos'!AW5)),IF(('Apostas - Grupos'!AV5-'Apostas - Grupos'!AW5)=('Jogos - Grupos'!F26-'Jogos - Grupos'!G26),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="Z5" s="106" t="str">
+      <c r="Z5" s="106">
         <f>IF(OR('Jogos - Grupos'!F27="",'Jogos - Grupos'!G27=""),"-",IF(OR('Apostas - Grupos'!AX5="",'Apostas - Grupos'!AY5=""),0,IF(AND('Apostas - Grupos'!AX5='Jogos - Grupos'!F27,'Apostas - Grupos'!AY5='Jogos - Grupos'!G27),5,IF(OR(AND('Jogos - Grupos'!F27='Jogos - Grupos'!G27,'Apostas - Grupos'!AX5='Apostas - Grupos'!AY5),AND('Jogos - Grupos'!F27&gt;'Jogos - Grupos'!G27,'Apostas - Grupos'!AX5&gt;'Apostas - Grupos'!AY5),AND('Jogos - Grupos'!F27&lt;'Jogos - Grupos'!G27,'Apostas - Grupos'!AX5&lt;'Apostas - Grupos'!AY5)),IF(('Apostas - Grupos'!AX5-'Apostas - Grupos'!AY5)=('Jogos - Grupos'!F27-'Jogos - Grupos'!G27),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F28="",'Jogos - Grupos'!G28=""),"-",IF(OR('Apostas - Grupos'!AZ5="",'Apostas - Grupos'!BA5=""),0,IF(AND('Apostas - Grupos'!AZ5='Jogos - Grupos'!F28,'Apostas - Grupos'!BA5='Jogos - Grupos'!G28),5,IF(OR(AND('Jogos - Grupos'!F28='Jogos - Grupos'!G28,'Apostas - Grupos'!AZ5='Apostas - Grupos'!BA5),AND('Jogos - Grupos'!F28&gt;'Jogos - Grupos'!G28,'Apostas - Grupos'!AZ5&gt;'Apostas - Grupos'!BA5),AND('Jogos - Grupos'!F28&lt;'Jogos - Grupos'!G28,'Apostas - Grupos'!AZ5&lt;'Apostas - Grupos'!BA5)),IF(('Apostas - Grupos'!AZ5-'Apostas - Grupos'!BA5)=('Jogos - Grupos'!F28-'Jogos - Grupos'!G28),3,2),0))))</f>
@@ -13693,9 +13697,9 @@
         <f>IF(OR('Jogos - Grupos'!F26="",'Jogos - Grupos'!G26=""),"-",IF(OR('Apostas - Grupos'!AV6="",'Apostas - Grupos'!AW6=""),0,IF(AND('Apostas - Grupos'!AV6='Jogos - Grupos'!F26,'Apostas - Grupos'!AW6='Jogos - Grupos'!G26),5,IF(OR(AND('Jogos - Grupos'!F26='Jogos - Grupos'!G26,'Apostas - Grupos'!AV6='Apostas - Grupos'!AW6),AND('Jogos - Grupos'!F26&gt;'Jogos - Grupos'!G26,'Apostas - Grupos'!AV6&gt;'Apostas - Grupos'!AW6),AND('Jogos - Grupos'!F26&lt;'Jogos - Grupos'!G26,'Apostas - Grupos'!AV6&lt;'Apostas - Grupos'!AW6)),IF(('Apostas - Grupos'!AV6-'Apostas - Grupos'!AW6)=('Jogos - Grupos'!F26-'Jogos - Grupos'!G26),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="Z6" s="108" t="str">
+      <c r="Z6" s="108">
         <f>IF(OR('Jogos - Grupos'!F27="",'Jogos - Grupos'!G27=""),"-",IF(OR('Apostas - Grupos'!AX6="",'Apostas - Grupos'!AY6=""),0,IF(AND('Apostas - Grupos'!AX6='Jogos - Grupos'!F27,'Apostas - Grupos'!AY6='Jogos - Grupos'!G27),5,IF(OR(AND('Jogos - Grupos'!F27='Jogos - Grupos'!G27,'Apostas - Grupos'!AX6='Apostas - Grupos'!AY6),AND('Jogos - Grupos'!F27&gt;'Jogos - Grupos'!G27,'Apostas - Grupos'!AX6&gt;'Apostas - Grupos'!AY6),AND('Jogos - Grupos'!F27&lt;'Jogos - Grupos'!G27,'Apostas - Grupos'!AX6&lt;'Apostas - Grupos'!AY6)),IF(('Apostas - Grupos'!AX6-'Apostas - Grupos'!AY6)=('Jogos - Grupos'!F27-'Jogos - Grupos'!G27),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F28="",'Jogos - Grupos'!G28=""),"-",IF(OR('Apostas - Grupos'!AZ6="",'Apostas - Grupos'!BA6=""),0,IF(AND('Apostas - Grupos'!AZ6='Jogos - Grupos'!F28,'Apostas - Grupos'!BA6='Jogos - Grupos'!G28),5,IF(OR(AND('Jogos - Grupos'!F28='Jogos - Grupos'!G28,'Apostas - Grupos'!AZ6='Apostas - Grupos'!BA6),AND('Jogos - Grupos'!F28&gt;'Jogos - Grupos'!G28,'Apostas - Grupos'!AZ6&gt;'Apostas - Grupos'!BA6),AND('Jogos - Grupos'!F28&lt;'Jogos - Grupos'!G28,'Apostas - Grupos'!AZ6&lt;'Apostas - Grupos'!BA6)),IF(('Apostas - Grupos'!AZ6-'Apostas - Grupos'!BA6)=('Jogos - Grupos'!F28-'Jogos - Grupos'!G28),3,2),0))))</f>
@@ -13990,9 +13994,9 @@
         <f>IF(OR('Jogos - Grupos'!F26="",'Jogos - Grupos'!G26=""),"-",IF(OR('Apostas - Grupos'!AV7="",'Apostas - Grupos'!AW7=""),0,IF(AND('Apostas - Grupos'!AV7='Jogos - Grupos'!F26,'Apostas - Grupos'!AW7='Jogos - Grupos'!G26),5,IF(OR(AND('Jogos - Grupos'!F26='Jogos - Grupos'!G26,'Apostas - Grupos'!AV7='Apostas - Grupos'!AW7),AND('Jogos - Grupos'!F26&gt;'Jogos - Grupos'!G26,'Apostas - Grupos'!AV7&gt;'Apostas - Grupos'!AW7),AND('Jogos - Grupos'!F26&lt;'Jogos - Grupos'!G26,'Apostas - Grupos'!AV7&lt;'Apostas - Grupos'!AW7)),IF(('Apostas - Grupos'!AV7-'Apostas - Grupos'!AW7)=('Jogos - Grupos'!F26-'Jogos - Grupos'!G26),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="Z7" s="106" t="str">
+      <c r="Z7" s="106">
         <f>IF(OR('Jogos - Grupos'!F27="",'Jogos - Grupos'!G27=""),"-",IF(OR('Apostas - Grupos'!AX7="",'Apostas - Grupos'!AY7=""),0,IF(AND('Apostas - Grupos'!AX7='Jogos - Grupos'!F27,'Apostas - Grupos'!AY7='Jogos - Grupos'!G27),5,IF(OR(AND('Jogos - Grupos'!F27='Jogos - Grupos'!G27,'Apostas - Grupos'!AX7='Apostas - Grupos'!AY7),AND('Jogos - Grupos'!F27&gt;'Jogos - Grupos'!G27,'Apostas - Grupos'!AX7&gt;'Apostas - Grupos'!AY7),AND('Jogos - Grupos'!F27&lt;'Jogos - Grupos'!G27,'Apostas - Grupos'!AX7&lt;'Apostas - Grupos'!AY7)),IF(('Apostas - Grupos'!AX7-'Apostas - Grupos'!AY7)=('Jogos - Grupos'!F27-'Jogos - Grupos'!G27),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F28="",'Jogos - Grupos'!G28=""),"-",IF(OR('Apostas - Grupos'!AZ7="",'Apostas - Grupos'!BA7=""),0,IF(AND('Apostas - Grupos'!AZ7='Jogos - Grupos'!F28,'Apostas - Grupos'!BA7='Jogos - Grupos'!G28),5,IF(OR(AND('Jogos - Grupos'!F28='Jogos - Grupos'!G28,'Apostas - Grupos'!AZ7='Apostas - Grupos'!BA7),AND('Jogos - Grupos'!F28&gt;'Jogos - Grupos'!G28,'Apostas - Grupos'!AZ7&gt;'Apostas - Grupos'!BA7),AND('Jogos - Grupos'!F28&lt;'Jogos - Grupos'!G28,'Apostas - Grupos'!AZ7&lt;'Apostas - Grupos'!BA7)),IF(('Apostas - Grupos'!AZ7-'Apostas - Grupos'!BA7)=('Jogos - Grupos'!F28-'Jogos - Grupos'!G28),3,2),0))))</f>
@@ -14287,9 +14291,9 @@
         <f>IF(OR('Jogos - Grupos'!F26="",'Jogos - Grupos'!G26=""),"-",IF(OR('Apostas - Grupos'!AV8="",'Apostas - Grupos'!AW8=""),0,IF(AND('Apostas - Grupos'!AV8='Jogos - Grupos'!F26,'Apostas - Grupos'!AW8='Jogos - Grupos'!G26),5,IF(OR(AND('Jogos - Grupos'!F26='Jogos - Grupos'!G26,'Apostas - Grupos'!AV8='Apostas - Grupos'!AW8),AND('Jogos - Grupos'!F26&gt;'Jogos - Grupos'!G26,'Apostas - Grupos'!AV8&gt;'Apostas - Grupos'!AW8),AND('Jogos - Grupos'!F26&lt;'Jogos - Grupos'!G26,'Apostas - Grupos'!AV8&lt;'Apostas - Grupos'!AW8)),IF(('Apostas - Grupos'!AV8-'Apostas - Grupos'!AW8)=('Jogos - Grupos'!F26-'Jogos - Grupos'!G26),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="Z8" s="108" t="str">
+      <c r="Z8" s="108">
         <f>IF(OR('Jogos - Grupos'!F27="",'Jogos - Grupos'!G27=""),"-",IF(OR('Apostas - Grupos'!AX8="",'Apostas - Grupos'!AY8=""),0,IF(AND('Apostas - Grupos'!AX8='Jogos - Grupos'!F27,'Apostas - Grupos'!AY8='Jogos - Grupos'!G27),5,IF(OR(AND('Jogos - Grupos'!F27='Jogos - Grupos'!G27,'Apostas - Grupos'!AX8='Apostas - Grupos'!AY8),AND('Jogos - Grupos'!F27&gt;'Jogos - Grupos'!G27,'Apostas - Grupos'!AX8&gt;'Apostas - Grupos'!AY8),AND('Jogos - Grupos'!F27&lt;'Jogos - Grupos'!G27,'Apostas - Grupos'!AX8&lt;'Apostas - Grupos'!AY8)),IF(('Apostas - Grupos'!AX8-'Apostas - Grupos'!AY8)=('Jogos - Grupos'!F27-'Jogos - Grupos'!G27),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F28="",'Jogos - Grupos'!G28=""),"-",IF(OR('Apostas - Grupos'!AZ8="",'Apostas - Grupos'!BA8=""),0,IF(AND('Apostas - Grupos'!AZ8='Jogos - Grupos'!F28,'Apostas - Grupos'!BA8='Jogos - Grupos'!G28),5,IF(OR(AND('Jogos - Grupos'!F28='Jogos - Grupos'!G28,'Apostas - Grupos'!AZ8='Apostas - Grupos'!BA8),AND('Jogos - Grupos'!F28&gt;'Jogos - Grupos'!G28,'Apostas - Grupos'!AZ8&gt;'Apostas - Grupos'!BA8),AND('Jogos - Grupos'!F28&lt;'Jogos - Grupos'!G28,'Apostas - Grupos'!AZ8&lt;'Apostas - Grupos'!BA8)),IF(('Apostas - Grupos'!AZ8-'Apostas - Grupos'!BA8)=('Jogos - Grupos'!F28-'Jogos - Grupos'!G28),3,2),0))))</f>
@@ -15273,7 +15277,7 @@
       </c>
       <c r="C19" s="118">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A19)*('Jogos - Grupos'!$D$3:$D$74=$B19)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A19)*('Jogos - Grupos'!$E$3:$E$74=$B19)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="118">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A19)*(('Jogos - Grupos'!$D$3:$D$74=$B19)+('Jogos - Grupos'!$E$3:$E$74=$B19))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -15281,23 +15285,23 @@
       </c>
       <c r="E19" s="118">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A19)*('Jogos - Grupos'!$D$3:$D$74=$B19)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A19)*('Jogos - Grupos'!$E$3:$E$74=$B19)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="118">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A19)*('Jogos - Grupos'!$D$3:$D$74=$B19)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A19)*('Jogos - Grupos'!$E$3:$E$74=$B19)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H19" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" s="118">
         <f t="shared" si="2"/>
-        <v>200000488</v>
+        <v>3206007488</v>
       </c>
       <c r="J19" s="29">
         <f>RANK(I19,$I$19:$I$22,0)</f>
@@ -15324,15 +15328,15 @@
       </c>
       <c r="E20" s="118">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A20)*('Jogos - Grupos'!$D$3:$D$74=$B20)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A20)*('Jogos - Grupos'!$E$3:$E$74=$B20)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="118">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A20)*('Jogos - Grupos'!$D$3:$D$74=$B20)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A20)*('Jogos - Grupos'!$E$3:$E$74=$B20)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G20" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="H20" s="29">
         <f t="shared" si="1"/>
@@ -15340,7 +15344,7 @@
       </c>
       <c r="I20" s="118">
         <f t="shared" si="2"/>
-        <v>200000417</v>
+        <v>194001417</v>
       </c>
       <c r="J20" s="29">
         <f>RANK(I20,$I$19:$I$22,0)</f>

--- a/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\projetos\bolão_copa\gabarito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B78E8AA-36C5-4E10-89B9-64B2AC722D41}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8804175F-FBC3-4213-9612-DE918B2EE506}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4976,67 +4976,73 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5045,22 +5051,13 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5076,6 +5073,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5836,7 +5836,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5972,67 +5972,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="273" t="s">
+      <c r="AH3" s="270" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="273" t="s">
+      <c r="AJ3" s="270" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="273" t="s">
+      <c r="AL3" s="270" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="273" t="s">
+      <c r="AN3" s="270" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="273" t="s">
+      <c r="AP3" s="270" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="273" t="s">
+      <c r="AR3" s="270" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="273" t="s">
+      <c r="AT3" s="270" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="273" t="s">
+      <c r="AV3" s="270" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="275" t="s">
+      <c r="AX3" s="274" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="275" t="s">
+      <c r="AZ3" s="274" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="275" t="s">
+      <c r="BB3" s="274" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="275" t="s">
+      <c r="BD3" s="274" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="281" t="s">
+      <c r="BF3" s="277" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="281" t="s">
+      <c r="BH3" s="277" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="279" t="s">
+      <c r="BJ3" s="273" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="280" t="s">
+      <c r="BL3" s="275" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -6041,131 +6041,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="270">
+      <c r="B4" s="272">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="270">
+      <c r="D4" s="272">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="270">
+      <c r="F4" s="272">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="270">
+      <c r="H4" s="272">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="270">
+      <c r="J4" s="272">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="270">
+      <c r="L4" s="272">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="270">
+      <c r="N4" s="272">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="270">
+      <c r="P4" s="272">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="270">
+      <c r="R4" s="272">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="270">
+      <c r="T4" s="272">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="270">
+      <c r="V4" s="272">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="270">
+      <c r="X4" s="272">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="270">
+      <c r="Z4" s="272">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="270">
+      <c r="AB4" s="272">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="270">
+      <c r="AD4" s="272">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="270">
+      <c r="AF4" s="272">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="274">
+      <c r="AH4" s="276">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="274">
+      <c r="AJ4" s="276">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="274">
+      <c r="AL4" s="276">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="274">
+      <c r="AN4" s="276">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="274">
+      <c r="AP4" s="276">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="274">
+      <c r="AR4" s="276">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="274">
+      <c r="AT4" s="276">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="274">
+      <c r="AV4" s="276">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="272">
+      <c r="AX4" s="278">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="272">
+      <c r="AZ4" s="278">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="272">
+      <c r="BB4" s="278">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="272">
+      <c r="BD4" s="278">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="277">
+      <c r="BF4" s="279">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="277">
+      <c r="BH4" s="279">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="276">
+      <c r="BJ4" s="281">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="278">
+      <c r="BL4" s="280">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7620,6 +7620,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="BJ4:BK4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
     <mergeCell ref="A2:BM2"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
@@ -7636,56 +7686,6 @@
     <mergeCell ref="BF3:BG3"/>
     <mergeCell ref="BH3:BI3"/>
     <mergeCell ref="V4:W4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="BJ4:BK4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7743,7 +7743,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8909,7 +8909,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8923,49 +8923,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1">
-      <c r="A4" s="284" t="s">
+      <c r="A4" s="289" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="284" t="s">
+      <c r="C4" s="289" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="284" t="s">
+      <c r="E4" s="289" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="284" t="s">
+      <c r="G4" s="289" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="284" t="s">
+      <c r="I4" s="289" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1">
-      <c r="A5" s="286" t="str">
+      <c r="A5" s="285" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="285">
+      <c r="C5" s="284">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="288">
+      <c r="E5" s="287">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="287">
+      <c r="G5" s="286">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="289" t="s">
+      <c r="I5" s="288" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9116,11 +9116,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9128,6 +9123,11 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9929,11 +9929,15 @@
       <c r="E33" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
+      <c r="F33" s="10">
+        <v>2</v>
+      </c>
+      <c r="G33" s="10">
+        <v>2</v>
+      </c>
       <c r="H33" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -11049,7 +11053,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11201,219 +11205,219 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="256" t="s">
+      <c r="B3" s="263" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="256" t="s">
+      <c r="D3" s="263" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="256" t="s">
+      <c r="F3" s="263" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="256" t="s">
+      <c r="H3" s="263" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="256" t="s">
+      <c r="J3" s="263" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="256" t="s">
+      <c r="L3" s="263" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="260" t="s">
+      <c r="N3" s="264" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="260" t="s">
+      <c r="P3" s="264" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="260" t="s">
+      <c r="R3" s="264" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="260" t="s">
+      <c r="T3" s="264" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="260" t="s">
+      <c r="V3" s="264" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="260" t="s">
+      <c r="X3" s="264" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="261" t="s">
+      <c r="Z3" s="259" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="261" t="s">
+      <c r="AB3" s="259" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="261" t="s">
+      <c r="AD3" s="259" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="261" t="s">
+      <c r="AF3" s="259" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="261" t="s">
+      <c r="AH3" s="259" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="261" t="s">
+      <c r="AJ3" s="259" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="257" t="s">
+      <c r="AL3" s="260" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="257" t="s">
+      <c r="AN3" s="260" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="257" t="s">
+      <c r="AP3" s="260" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="257" t="s">
+      <c r="AR3" s="260" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="257" t="s">
+      <c r="AT3" s="260" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="257" t="s">
+      <c r="AV3" s="260" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="258" t="s">
+      <c r="AX3" s="265" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="258" t="s">
+      <c r="AZ3" s="265" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="258" t="s">
+      <c r="BB3" s="265" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="258" t="s">
+      <c r="BD3" s="265" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="258" t="s">
+      <c r="BF3" s="265" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="258" t="s">
+      <c r="BH3" s="265" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="262" t="s">
+      <c r="BJ3" s="266" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="262" t="s">
+      <c r="BL3" s="266" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="262" t="s">
+      <c r="BN3" s="266" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="262" t="s">
+      <c r="BP3" s="266" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="262" t="s">
+      <c r="BR3" s="266" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="262" t="s">
+      <c r="BT3" s="266" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
-      <c r="BV3" s="263" t="s">
+      <c r="BV3" s="256" t="s">
         <v>224</v>
       </c>
       <c r="BW3" s="253"/>
-      <c r="BX3" s="263" t="s">
+      <c r="BX3" s="256" t="s">
         <v>225</v>
       </c>
       <c r="BY3" s="253"/>
-      <c r="BZ3" s="263" t="s">
+      <c r="BZ3" s="256" t="s">
         <v>226</v>
       </c>
       <c r="CA3" s="253"/>
-      <c r="CB3" s="263" t="s">
+      <c r="CB3" s="256" t="s">
         <v>227</v>
       </c>
       <c r="CC3" s="253"/>
-      <c r="CD3" s="263" t="s">
+      <c r="CD3" s="256" t="s">
         <v>228</v>
       </c>
       <c r="CE3" s="253"/>
-      <c r="CF3" s="263" t="s">
+      <c r="CF3" s="256" t="s">
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="259" t="s">
+      <c r="CH3" s="257" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="259" t="s">
+      <c r="CJ3" s="257" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="259" t="s">
+      <c r="CL3" s="257" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="259" t="s">
+      <c r="CN3" s="257" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="259" t="s">
+      <c r="CP3" s="257" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="259" t="s">
+      <c r="CR3" s="257" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
-      <c r="CT3" s="265" t="s">
+      <c r="CT3" s="258" t="s">
         <v>236</v>
       </c>
       <c r="CU3" s="253"/>
-      <c r="CV3" s="265" t="s">
+      <c r="CV3" s="258" t="s">
         <v>237</v>
       </c>
       <c r="CW3" s="253"/>
-      <c r="CX3" s="265" t="s">
+      <c r="CX3" s="258" t="s">
         <v>238</v>
       </c>
       <c r="CY3" s="253"/>
-      <c r="CZ3" s="265" t="s">
+      <c r="CZ3" s="258" t="s">
         <v>239</v>
       </c>
       <c r="DA3" s="253"/>
-      <c r="DB3" s="265" t="s">
+      <c r="DB3" s="258" t="s">
         <v>240</v>
       </c>
       <c r="DC3" s="253"/>
-      <c r="DD3" s="265" t="s">
+      <c r="DD3" s="258" t="s">
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
@@ -11441,51 +11445,51 @@
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="266" t="s">
+      <c r="DR3" s="268" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="266" t="s">
+      <c r="DT3" s="268" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="266" t="s">
+      <c r="DV3" s="268" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="266" t="s">
+      <c r="DX3" s="268" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="266" t="s">
+      <c r="DZ3" s="268" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="266" t="s">
+      <c r="EB3" s="268" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="264" t="s">
+      <c r="ED3" s="262" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="264" t="s">
+      <c r="EF3" s="262" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="264" t="s">
+      <c r="EH3" s="262" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="264" t="s">
+      <c r="EJ3" s="262" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="264" t="s">
+      <c r="EL3" s="262" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="264" t="s">
+      <c r="EN3" s="262" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12525,16 +12529,54 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="CJ3:CK3"/>
+    <mergeCell ref="CL3:CM3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="BT3:BU3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="CF3:CG3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="DN3:DO3"/>
+    <mergeCell ref="A1:EO1"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="CR3:CS3"/>
     <mergeCell ref="A2:EO2"/>
     <mergeCell ref="EJ3:EK3"/>
     <mergeCell ref="D3:E3"/>
@@ -12551,54 +12593,16 @@
     <mergeCell ref="DJ3:DK3"/>
     <mergeCell ref="EL3:EM3"/>
     <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="A1:EO1"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="CJ3:CK3"/>
-    <mergeCell ref="CL3:CM3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="BT3:BU3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="CF3:CG3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="CT3:CU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12624,7 +12628,7 @@
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12777,7 +12781,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>
@@ -13424,9 +13428,9 @@
         <f>IF(OR('Jogos - Grupos'!F32="",'Jogos - Grupos'!G32=""),"-",IF(OR('Apostas - Grupos'!BH5="",'Apostas - Grupos'!BI5=""),0,IF(AND('Apostas - Grupos'!BH5='Jogos - Grupos'!F32,'Apostas - Grupos'!BI5='Jogos - Grupos'!G32),5,IF(OR(AND('Jogos - Grupos'!F32='Jogos - Grupos'!G32,'Apostas - Grupos'!BH5='Apostas - Grupos'!BI5),AND('Jogos - Grupos'!F32&gt;'Jogos - Grupos'!G32,'Apostas - Grupos'!BH5&gt;'Apostas - Grupos'!BI5),AND('Jogos - Grupos'!F32&lt;'Jogos - Grupos'!G32,'Apostas - Grupos'!BH5&lt;'Apostas - Grupos'!BI5)),IF(('Apostas - Grupos'!BH5-'Apostas - Grupos'!BI5)=('Jogos - Grupos'!F32-'Jogos - Grupos'!G32),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="AF5" s="106" t="str">
+      <c r="AF5" s="106">
         <f>IF(OR('Jogos - Grupos'!F33="",'Jogos - Grupos'!G33=""),"-",IF(OR('Apostas - Grupos'!BJ5="",'Apostas - Grupos'!BK5=""),0,IF(AND('Apostas - Grupos'!BJ5='Jogos - Grupos'!F33,'Apostas - Grupos'!BK5='Jogos - Grupos'!G33),5,IF(OR(AND('Jogos - Grupos'!F33='Jogos - Grupos'!G33,'Apostas - Grupos'!BJ5='Apostas - Grupos'!BK5),AND('Jogos - Grupos'!F33&gt;'Jogos - Grupos'!G33,'Apostas - Grupos'!BJ5&gt;'Apostas - Grupos'!BK5),AND('Jogos - Grupos'!F33&lt;'Jogos - Grupos'!G33,'Apostas - Grupos'!BJ5&lt;'Apostas - Grupos'!BK5)),IF(('Apostas - Grupos'!BJ5-'Apostas - Grupos'!BK5)=('Jogos - Grupos'!F33-'Jogos - Grupos'!G33),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F34="",'Jogos - Grupos'!G34=""),"-",IF(OR('Apostas - Grupos'!BL5="",'Apostas - Grupos'!BM5=""),0,IF(AND('Apostas - Grupos'!BL5='Jogos - Grupos'!F34,'Apostas - Grupos'!BM5='Jogos - Grupos'!G34),5,IF(OR(AND('Jogos - Grupos'!F34='Jogos - Grupos'!G34,'Apostas - Grupos'!BL5='Apostas - Grupos'!BM5),AND('Jogos - Grupos'!F34&gt;'Jogos - Grupos'!G34,'Apostas - Grupos'!BL5&gt;'Apostas - Grupos'!BM5),AND('Jogos - Grupos'!F34&lt;'Jogos - Grupos'!G34,'Apostas - Grupos'!BL5&lt;'Apostas - Grupos'!BM5)),IF(('Apostas - Grupos'!BL5-'Apostas - Grupos'!BM5)=('Jogos - Grupos'!F34-'Jogos - Grupos'!G34),3,2),0))))</f>
@@ -13721,9 +13725,9 @@
         <f>IF(OR('Jogos - Grupos'!F32="",'Jogos - Grupos'!G32=""),"-",IF(OR('Apostas - Grupos'!BH6="",'Apostas - Grupos'!BI6=""),0,IF(AND('Apostas - Grupos'!BH6='Jogos - Grupos'!F32,'Apostas - Grupos'!BI6='Jogos - Grupos'!G32),5,IF(OR(AND('Jogos - Grupos'!F32='Jogos - Grupos'!G32,'Apostas - Grupos'!BH6='Apostas - Grupos'!BI6),AND('Jogos - Grupos'!F32&gt;'Jogos - Grupos'!G32,'Apostas - Grupos'!BH6&gt;'Apostas - Grupos'!BI6),AND('Jogos - Grupos'!F32&lt;'Jogos - Grupos'!G32,'Apostas - Grupos'!BH6&lt;'Apostas - Grupos'!BI6)),IF(('Apostas - Grupos'!BH6-'Apostas - Grupos'!BI6)=('Jogos - Grupos'!F32-'Jogos - Grupos'!G32),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="AF6" s="108" t="str">
+      <c r="AF6" s="108">
         <f>IF(OR('Jogos - Grupos'!F33="",'Jogos - Grupos'!G33=""),"-",IF(OR('Apostas - Grupos'!BJ6="",'Apostas - Grupos'!BK6=""),0,IF(AND('Apostas - Grupos'!BJ6='Jogos - Grupos'!F33,'Apostas - Grupos'!BK6='Jogos - Grupos'!G33),5,IF(OR(AND('Jogos - Grupos'!F33='Jogos - Grupos'!G33,'Apostas - Grupos'!BJ6='Apostas - Grupos'!BK6),AND('Jogos - Grupos'!F33&gt;'Jogos - Grupos'!G33,'Apostas - Grupos'!BJ6&gt;'Apostas - Grupos'!BK6),AND('Jogos - Grupos'!F33&lt;'Jogos - Grupos'!G33,'Apostas - Grupos'!BJ6&lt;'Apostas - Grupos'!BK6)),IF(('Apostas - Grupos'!BJ6-'Apostas - Grupos'!BK6)=('Jogos - Grupos'!F33-'Jogos - Grupos'!G33),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F34="",'Jogos - Grupos'!G34=""),"-",IF(OR('Apostas - Grupos'!BL6="",'Apostas - Grupos'!BM6=""),0,IF(AND('Apostas - Grupos'!BL6='Jogos - Grupos'!F34,'Apostas - Grupos'!BM6='Jogos - Grupos'!G34),5,IF(OR(AND('Jogos - Grupos'!F34='Jogos - Grupos'!G34,'Apostas - Grupos'!BL6='Apostas - Grupos'!BM6),AND('Jogos - Grupos'!F34&gt;'Jogos - Grupos'!G34,'Apostas - Grupos'!BL6&gt;'Apostas - Grupos'!BM6),AND('Jogos - Grupos'!F34&lt;'Jogos - Grupos'!G34,'Apostas - Grupos'!BL6&lt;'Apostas - Grupos'!BM6)),IF(('Apostas - Grupos'!BL6-'Apostas - Grupos'!BM6)=('Jogos - Grupos'!F34-'Jogos - Grupos'!G34),3,2),0))))</f>
@@ -14018,9 +14022,9 @@
         <f>IF(OR('Jogos - Grupos'!F32="",'Jogos - Grupos'!G32=""),"-",IF(OR('Apostas - Grupos'!BH7="",'Apostas - Grupos'!BI7=""),0,IF(AND('Apostas - Grupos'!BH7='Jogos - Grupos'!F32,'Apostas - Grupos'!BI7='Jogos - Grupos'!G32),5,IF(OR(AND('Jogos - Grupos'!F32='Jogos - Grupos'!G32,'Apostas - Grupos'!BH7='Apostas - Grupos'!BI7),AND('Jogos - Grupos'!F32&gt;'Jogos - Grupos'!G32,'Apostas - Grupos'!BH7&gt;'Apostas - Grupos'!BI7),AND('Jogos - Grupos'!F32&lt;'Jogos - Grupos'!G32,'Apostas - Grupos'!BH7&lt;'Apostas - Grupos'!BI7)),IF(('Apostas - Grupos'!BH7-'Apostas - Grupos'!BI7)=('Jogos - Grupos'!F32-'Jogos - Grupos'!G32),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="AF7" s="106" t="str">
+      <c r="AF7" s="106">
         <f>IF(OR('Jogos - Grupos'!F33="",'Jogos - Grupos'!G33=""),"-",IF(OR('Apostas - Grupos'!BJ7="",'Apostas - Grupos'!BK7=""),0,IF(AND('Apostas - Grupos'!BJ7='Jogos - Grupos'!F33,'Apostas - Grupos'!BK7='Jogos - Grupos'!G33),5,IF(OR(AND('Jogos - Grupos'!F33='Jogos - Grupos'!G33,'Apostas - Grupos'!BJ7='Apostas - Grupos'!BK7),AND('Jogos - Grupos'!F33&gt;'Jogos - Grupos'!G33,'Apostas - Grupos'!BJ7&gt;'Apostas - Grupos'!BK7),AND('Jogos - Grupos'!F33&lt;'Jogos - Grupos'!G33,'Apostas - Grupos'!BJ7&lt;'Apostas - Grupos'!BK7)),IF(('Apostas - Grupos'!BJ7-'Apostas - Grupos'!BK7)=('Jogos - Grupos'!F33-'Jogos - Grupos'!G33),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F34="",'Jogos - Grupos'!G34=""),"-",IF(OR('Apostas - Grupos'!BL7="",'Apostas - Grupos'!BM7=""),0,IF(AND('Apostas - Grupos'!BL7='Jogos - Grupos'!F34,'Apostas - Grupos'!BM7='Jogos - Grupos'!G34),5,IF(OR(AND('Jogos - Grupos'!F34='Jogos - Grupos'!G34,'Apostas - Grupos'!BL7='Apostas - Grupos'!BM7),AND('Jogos - Grupos'!F34&gt;'Jogos - Grupos'!G34,'Apostas - Grupos'!BL7&gt;'Apostas - Grupos'!BM7),AND('Jogos - Grupos'!F34&lt;'Jogos - Grupos'!G34,'Apostas - Grupos'!BL7&lt;'Apostas - Grupos'!BM7)),IF(('Apostas - Grupos'!BL7-'Apostas - Grupos'!BM7)=('Jogos - Grupos'!F34-'Jogos - Grupos'!G34),3,2),0))))</f>
@@ -14315,9 +14319,9 @@
         <f>IF(OR('Jogos - Grupos'!F32="",'Jogos - Grupos'!G32=""),"-",IF(OR('Apostas - Grupos'!BH8="",'Apostas - Grupos'!BI8=""),0,IF(AND('Apostas - Grupos'!BH8='Jogos - Grupos'!F32,'Apostas - Grupos'!BI8='Jogos - Grupos'!G32),5,IF(OR(AND('Jogos - Grupos'!F32='Jogos - Grupos'!G32,'Apostas - Grupos'!BH8='Apostas - Grupos'!BI8),AND('Jogos - Grupos'!F32&gt;'Jogos - Grupos'!G32,'Apostas - Grupos'!BH8&gt;'Apostas - Grupos'!BI8),AND('Jogos - Grupos'!F32&lt;'Jogos - Grupos'!G32,'Apostas - Grupos'!BH8&lt;'Apostas - Grupos'!BI8)),IF(('Apostas - Grupos'!BH8-'Apostas - Grupos'!BI8)=('Jogos - Grupos'!F32-'Jogos - Grupos'!G32),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="AF8" s="108" t="str">
+      <c r="AF8" s="108">
         <f>IF(OR('Jogos - Grupos'!F33="",'Jogos - Grupos'!G33=""),"-",IF(OR('Apostas - Grupos'!BJ8="",'Apostas - Grupos'!BK8=""),0,IF(AND('Apostas - Grupos'!BJ8='Jogos - Grupos'!F33,'Apostas - Grupos'!BK8='Jogos - Grupos'!G33),5,IF(OR(AND('Jogos - Grupos'!F33='Jogos - Grupos'!G33,'Apostas - Grupos'!BJ8='Apostas - Grupos'!BK8),AND('Jogos - Grupos'!F33&gt;'Jogos - Grupos'!G33,'Apostas - Grupos'!BJ8&gt;'Apostas - Grupos'!BK8),AND('Jogos - Grupos'!F33&lt;'Jogos - Grupos'!G33,'Apostas - Grupos'!BJ8&lt;'Apostas - Grupos'!BK8)),IF(('Apostas - Grupos'!BJ8-'Apostas - Grupos'!BK8)=('Jogos - Grupos'!F33-'Jogos - Grupos'!G33),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F34="",'Jogos - Grupos'!G34=""),"-",IF(OR('Apostas - Grupos'!BL8="",'Apostas - Grupos'!BM8=""),0,IF(AND('Apostas - Grupos'!BL8='Jogos - Grupos'!F34,'Apostas - Grupos'!BM8='Jogos - Grupos'!G34),5,IF(OR(AND('Jogos - Grupos'!F34='Jogos - Grupos'!G34,'Apostas - Grupos'!BL8='Apostas - Grupos'!BM8),AND('Jogos - Grupos'!F34&gt;'Jogos - Grupos'!G34,'Apostas - Grupos'!BL8&gt;'Apostas - Grupos'!BM8),AND('Jogos - Grupos'!F34&lt;'Jogos - Grupos'!G34,'Apostas - Grupos'!BL8&lt;'Apostas - Grupos'!BM8)),IF(('Apostas - Grupos'!BL8-'Apostas - Grupos'!BM8)=('Jogos - Grupos'!F34-'Jogos - Grupos'!G34),3,2),0))))</f>
@@ -15453,15 +15457,15 @@
       </c>
       <c r="D23" s="120">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A23)*(('Jogos - Grupos'!$D$3:$D$74=$B23)+('Jogos - Grupos'!$E$3:$E$74=$B23))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="120">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A23)*('Jogos - Grupos'!$D$3:$D$74=$B23)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A23)*('Jogos - Grupos'!$E$3:$E$74=$B23)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="120">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A23)*('Jogos - Grupos'!$D$3:$D$74=$B23)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A23)*('Jogos - Grupos'!$E$3:$E$74=$B23)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="120">
         <f t="shared" si="0"/>
@@ -15469,11 +15473,11 @@
       </c>
       <c r="H23" s="34">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="120">
         <f t="shared" si="2"/>
-        <v>200000492</v>
+        <v>1200002492</v>
       </c>
       <c r="J23" s="34">
         <f>RANK(I23,$I$23:$I$26,0)</f>
@@ -15496,15 +15500,15 @@
       </c>
       <c r="D24" s="120">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A24)*(('Jogos - Grupos'!$D$3:$D$74=$B24)+('Jogos - Grupos'!$E$3:$E$74=$B24))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="120">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A24)*('Jogos - Grupos'!$D$3:$D$74=$B24)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A24)*('Jogos - Grupos'!$E$3:$E$74=$B24)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" s="120">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A24)*('Jogos - Grupos'!$D$3:$D$74=$B24)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A24)*('Jogos - Grupos'!$E$3:$E$74=$B24)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="120">
         <f t="shared" si="0"/>
@@ -15512,11 +15516,11 @@
       </c>
       <c r="H24" s="34">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="120">
         <f t="shared" si="2"/>
-        <v>200000485</v>
+        <v>1200002485</v>
       </c>
       <c r="J24" s="34">
         <f>RANK(I24,$I$23:$I$26,0)</f>
